--- a/Data/craft learning1.xlsx
+++ b/Data/craft learning1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FilesVC\HRAF-2022\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E30294-F353-4DBC-B913-0419A7CEDCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67989961-3178-42CC-A895-AEAF67DEF996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="craft learning" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'craft learning'!$W$1:$W$488</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'craft learning'!$W$1:$W$489</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14606" uniqueCount="1758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14825" uniqueCount="1758">
   <si>
     <t>Area</t>
   </si>
@@ -6174,7 +6174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE488"/>
+  <dimension ref="A1:AE489"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.73046875" customWidth="1"/>
@@ -34767,9 +34767,11 @@
         <v>27</v>
       </c>
       <c r="W301" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="X301" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="X301" s="1"/>
       <c r="Y301" s="1" t="s">
         <v>1541</v>
       </c>
@@ -34862,7 +34864,9 @@
       <c r="W302" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X302" s="1"/>
+      <c r="X302" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y302" s="1" t="s">
         <v>27</v>
       </c>
@@ -34953,9 +34957,11 @@
         <v>27</v>
       </c>
       <c r="W303" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="X303" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="X303" s="1"/>
       <c r="Y303" s="1" t="s">
         <v>27</v>
       </c>
@@ -35048,7 +35054,9 @@
       <c r="W304" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X304" s="1"/>
+      <c r="X304" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y304" s="1" t="s">
         <v>27</v>
       </c>
@@ -35141,7 +35149,9 @@
       <c r="W305" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X305" s="1"/>
+      <c r="X305" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y305" s="1" t="s">
         <v>27</v>
       </c>
@@ -35234,7 +35244,9 @@
       <c r="W306" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X306" s="1"/>
+      <c r="X306" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y306" s="1" t="s">
         <v>27</v>
       </c>
@@ -35327,7 +35339,9 @@
       <c r="W307" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="X307" s="1"/>
+      <c r="X307" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y307" s="1" t="s">
         <v>1541</v>
       </c>
@@ -35420,7 +35434,9 @@
       <c r="W308" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X308" s="1"/>
+      <c r="X308" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y308" s="1" t="s">
         <v>27</v>
       </c>
@@ -35513,7 +35529,9 @@
       <c r="W309" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X309" s="1"/>
+      <c r="X309" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y309" s="1" t="s">
         <v>1541</v>
       </c>
@@ -35606,7 +35624,9 @@
       <c r="W310" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="X310" s="1"/>
+      <c r="X310" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y310" s="1" t="s">
         <v>27</v>
       </c>
@@ -35629,96 +35649,98 @@
         <v>953</v>
       </c>
     </row>
-    <row r="311" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A311" s="1" t="s">
+    <row r="311" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A311" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="B311" s="1" t="s">
+      <c r="B311" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="C311" s="1" t="s">
+      <c r="C311" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="D311" s="1" t="s">
+      <c r="D311" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E311" s="1" t="s">
+      <c r="E311" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="F311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H311" s="1" t="s">
+      <c r="F311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H311" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="I311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L311" s="1" t="s">
+      <c r="I311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L311" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M311" s="1">
+      <c r="M311" s="5">
         <v>1</v>
       </c>
-      <c r="N311" s="1" t="s">
+      <c r="N311" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="O311" s="1" t="s">
+      <c r="O311" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P311" s="1" t="s">
+      <c r="P311" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Q311" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R311" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W311" s="1" t="s">
+      <c r="Q311" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R311" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="T311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="U311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="W311" s="5" t="s">
         <v>1516</v>
       </c>
-      <c r="X311" s="1"/>
-      <c r="Y311" s="1" t="s">
+      <c r="X311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y311" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="Z311" s="1" t="s">
+      <c r="Z311" s="5" t="s">
         <v>1536</v>
       </c>
-      <c r="AA311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD311" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE311" s="1" t="s">
+      <c r="AA311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE311" s="5" t="s">
         <v>954</v>
       </c>
     </row>
@@ -35790,9 +35812,11 @@
         <v>27</v>
       </c>
       <c r="W312" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="X312" s="1" t="s">
         <v>1517</v>
       </c>
-      <c r="X312" s="1"/>
       <c r="Y312" s="1" t="s">
         <v>27</v>
       </c>
@@ -35885,7 +35909,9 @@
       <c r="W313" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X313" s="1"/>
+      <c r="X313" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y313" s="1" t="s">
         <v>1541</v>
       </c>
@@ -35978,7 +36004,9 @@
       <c r="W314" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X314" s="1"/>
+      <c r="X314" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y314" s="1" t="s">
         <v>27</v>
       </c>
@@ -36071,7 +36099,9 @@
       <c r="W315" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X315" s="1"/>
+      <c r="X315" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y315" s="1" t="s">
         <v>27</v>
       </c>
@@ -36164,7 +36194,9 @@
       <c r="W316" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X316" s="1"/>
+      <c r="X316" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y316" s="1" t="s">
         <v>1547</v>
       </c>
@@ -36257,7 +36289,9 @@
       <c r="W317" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X317" s="1"/>
+      <c r="X317" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y317" s="1" t="s">
         <v>27</v>
       </c>
@@ -36350,7 +36384,9 @@
       <c r="W318" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X318" s="1"/>
+      <c r="X318" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y318" s="1" t="s">
         <v>1541</v>
       </c>
@@ -36441,9 +36477,11 @@
         <v>27</v>
       </c>
       <c r="W319" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="X319" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="X319" s="1"/>
       <c r="Y319" s="1" t="s">
         <v>27</v>
       </c>
@@ -36536,7 +36574,9 @@
       <c r="W320" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="X320" s="1"/>
+      <c r="X320" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y320" s="1" t="s">
         <v>1568</v>
       </c>
@@ -36629,7 +36669,9 @@
       <c r="W321" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X321" s="1"/>
+      <c r="X321" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y321" s="1" t="s">
         <v>1547</v>
       </c>
@@ -36722,7 +36764,9 @@
       <c r="W322" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X322" s="1"/>
+      <c r="X322" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y322" s="1" t="s">
         <v>27</v>
       </c>
@@ -36813,9 +36857,11 @@
         <v>27</v>
       </c>
       <c r="W323" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="X323" s="1" t="s">
         <v>1518</v>
       </c>
-      <c r="X323" s="1"/>
       <c r="Y323" s="1" t="s">
         <v>27</v>
       </c>
@@ -36906,9 +36952,11 @@
         <v>27</v>
       </c>
       <c r="W324" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="X324" s="1" t="s">
         <v>1670</v>
       </c>
-      <c r="X324" s="1"/>
       <c r="Y324" s="1" t="s">
         <v>27</v>
       </c>
@@ -37001,7 +37049,9 @@
       <c r="W325" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="X325" s="1"/>
+      <c r="X325" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y325" s="1" t="s">
         <v>1541</v>
       </c>
@@ -37092,9 +37142,11 @@
         <v>27</v>
       </c>
       <c r="W326" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="X326" s="1" t="s">
         <v>1671</v>
       </c>
-      <c r="X326" s="1"/>
       <c r="Y326" s="1" t="s">
         <v>27</v>
       </c>
@@ -37187,7 +37239,9 @@
       <c r="W327" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X327" s="1"/>
+      <c r="X327" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y327" s="1" t="s">
         <v>27</v>
       </c>
@@ -37278,9 +37332,11 @@
         <v>27</v>
       </c>
       <c r="W328" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="X328" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="X328" s="1"/>
       <c r="Y328" s="1" t="s">
         <v>995</v>
       </c>
@@ -37373,7 +37429,9 @@
       <c r="W329" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X329" s="1"/>
+      <c r="X329" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y329" s="1" t="s">
         <v>27</v>
       </c>
@@ -37466,7 +37524,9 @@
       <c r="W330" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="X330" s="1"/>
+      <c r="X330" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y330" s="1" t="s">
         <v>27</v>
       </c>
@@ -37559,7 +37619,9 @@
       <c r="W331" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X331" s="1"/>
+      <c r="X331" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y331" s="1" t="s">
         <v>1547</v>
       </c>
@@ -37652,7 +37714,9 @@
       <c r="W332" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X332" s="1"/>
+      <c r="X332" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y332" s="1" t="s">
         <v>1541</v>
       </c>
@@ -37745,7 +37809,9 @@
       <c r="W333" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X333" s="1"/>
+      <c r="X333" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y333" s="1" t="s">
         <v>1547</v>
       </c>
@@ -37836,9 +37902,11 @@
         <v>27</v>
       </c>
       <c r="W334" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="X334" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="X334" s="1"/>
       <c r="Y334" s="1" t="s">
         <v>27</v>
       </c>
@@ -37931,7 +37999,9 @@
       <c r="W335" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X335" s="1"/>
+      <c r="X335" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y335" s="1" t="s">
         <v>27</v>
       </c>
@@ -38024,7 +38094,9 @@
       <c r="W336" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X336" s="1"/>
+      <c r="X336" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y336" s="1" t="s">
         <v>1541</v>
       </c>
@@ -38117,7 +38189,9 @@
       <c r="W337" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X337" s="1"/>
+      <c r="X337" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y337" s="1" t="s">
         <v>1547</v>
       </c>
@@ -38210,7 +38284,9 @@
       <c r="W338" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X338" s="1"/>
+      <c r="X338" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y338" s="1" t="s">
         <v>27</v>
       </c>
@@ -38303,7 +38379,9 @@
       <c r="W339" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X339" s="1"/>
+      <c r="X339" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y339" s="1" t="s">
         <v>27</v>
       </c>
@@ -38396,7 +38474,9 @@
       <c r="W340" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X340" s="1"/>
+      <c r="X340" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y340" s="1" t="s">
         <v>27</v>
       </c>
@@ -38489,7 +38569,9 @@
       <c r="W341" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="X341" s="1"/>
+      <c r="X341" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y341" s="1" t="s">
         <v>1541</v>
       </c>
@@ -38582,7 +38664,9 @@
       <c r="W342" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="X342" s="1"/>
+      <c r="X342" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y342" s="1" t="s">
         <v>1541</v>
       </c>
@@ -38675,7 +38759,9 @@
       <c r="W343" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X343" s="1"/>
+      <c r="X343" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y343" s="1" t="s">
         <v>1541</v>
       </c>
@@ -38768,7 +38854,9 @@
       <c r="W344" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X344" s="1"/>
+      <c r="X344" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y344" s="1" t="s">
         <v>27</v>
       </c>
@@ -38861,7 +38949,9 @@
       <c r="W345" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="X345" s="1"/>
+      <c r="X345" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y345" s="1" t="s">
         <v>27</v>
       </c>
@@ -38954,7 +39044,9 @@
       <c r="W346" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X346" s="1"/>
+      <c r="X346" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y346" s="1" t="s">
         <v>27</v>
       </c>
@@ -39045,9 +39137,11 @@
         <v>27</v>
       </c>
       <c r="W347" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="X347" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="X347" s="1"/>
       <c r="Y347" s="1" t="s">
         <v>1568</v>
       </c>
@@ -39140,7 +39234,9 @@
       <c r="W348" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X348" s="1"/>
+      <c r="X348" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y348" s="1" t="s">
         <v>1547</v>
       </c>
@@ -39233,7 +39329,9 @@
       <c r="W349" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X349" s="1"/>
+      <c r="X349" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y349" s="1" t="s">
         <v>266</v>
       </c>
@@ -39326,7 +39424,9 @@
       <c r="W350" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X350" s="1"/>
+      <c r="X350" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y350" s="1" t="s">
         <v>266</v>
       </c>
@@ -39419,7 +39519,9 @@
       <c r="W351" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X351" s="1"/>
+      <c r="X351" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y351" s="1" t="s">
         <v>266</v>
       </c>
@@ -39512,7 +39614,9 @@
       <c r="W352" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X352" s="1"/>
+      <c r="X352" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y352" s="1" t="s">
         <v>1541</v>
       </c>
@@ -39605,7 +39709,9 @@
       <c r="W353" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X353" s="1"/>
+      <c r="X353" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y353" s="1" t="s">
         <v>27</v>
       </c>
@@ -39698,7 +39804,9 @@
       <c r="W354" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="X354" s="1"/>
+      <c r="X354" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y354" s="1" t="s">
         <v>1541</v>
       </c>
@@ -39789,9 +39897,11 @@
         <v>27</v>
       </c>
       <c r="W355" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="X355" s="1" t="s">
         <v>1519</v>
       </c>
-      <c r="X355" s="1"/>
       <c r="Y355" s="1" t="s">
         <v>27</v>
       </c>
@@ -39814,96 +39924,98 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="356" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A356" s="1" t="s">
+    <row r="356" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A356" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="B356" s="1" t="s">
+      <c r="B356" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C356" s="1" t="s">
+      <c r="C356" s="5" t="s">
         <v>1092</v>
       </c>
-      <c r="D356" s="1" t="s">
+      <c r="D356" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E356" s="1" t="s">
+      <c r="E356" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F356" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G356" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H356" s="1" t="s">
+      <c r="F356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H356" s="5" t="s">
         <v>1093</v>
       </c>
-      <c r="I356" s="1" t="s">
+      <c r="I356" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="J356" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K356" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L356" s="1" t="s">
+      <c r="J356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L356" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M356" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N356" s="1" t="s">
+      <c r="M356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N356" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="O356" s="1" t="s">
+      <c r="O356" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P356" s="1" t="s">
+      <c r="P356" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="Q356" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R356" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S356" s="1" t="s">
+      <c r="Q356" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R356" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S356" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="T356" s="1" t="s">
+      <c r="T356" s="5" t="s">
         <v>1545</v>
       </c>
-      <c r="U356" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V356" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W356" s="1" t="s">
+      <c r="U356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="W356" s="5" t="s">
         <v>1673</v>
       </c>
-      <c r="X356" s="1"/>
-      <c r="Y356" s="1" t="s">
+      <c r="X356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y356" s="5" t="s">
         <v>1615</v>
       </c>
-      <c r="Z356" s="1" t="s">
+      <c r="Z356" s="5" t="s">
         <v>1536</v>
       </c>
-      <c r="AA356" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB356" s="1" t="s">
+      <c r="AA356" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB356" s="5" t="s">
         <v>1537</v>
       </c>
-      <c r="AC356" s="1" t="s">
+      <c r="AC356" s="5" t="s">
         <v>1543</v>
       </c>
-      <c r="AD356" s="1" t="s">
+      <c r="AD356" s="5" t="s">
         <v>1094</v>
       </c>
-      <c r="AE356" s="1" t="s">
+      <c r="AE356" s="5" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -39975,9 +40087,11 @@
         <v>27</v>
       </c>
       <c r="W357" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="X357" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="X357" s="1"/>
       <c r="Y357" s="1" t="s">
         <v>266</v>
       </c>
@@ -40068,9 +40182,11 @@
         <v>27</v>
       </c>
       <c r="W358" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="X358" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="X358" s="1"/>
       <c r="Y358" s="1" t="s">
         <v>27</v>
       </c>
@@ -40163,7 +40279,9 @@
       <c r="W359" s="1" t="s">
         <v>1621</v>
       </c>
-      <c r="X359" s="1"/>
+      <c r="X359" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y359" s="1" t="s">
         <v>27</v>
       </c>
@@ -40256,7 +40374,9 @@
       <c r="W360" s="1" t="s">
         <v>1678</v>
       </c>
-      <c r="X360" s="1"/>
+      <c r="X360" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y360" s="1" t="s">
         <v>27</v>
       </c>
@@ -40347,9 +40467,11 @@
         <v>27</v>
       </c>
       <c r="W361" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="X361" s="1" t="s">
         <v>1520</v>
       </c>
-      <c r="X361" s="1"/>
       <c r="Y361" s="1" t="s">
         <v>266</v>
       </c>
@@ -40442,7 +40564,9 @@
       <c r="W362" s="1" t="s">
         <v>1679</v>
       </c>
-      <c r="X362" s="1"/>
+      <c r="X362" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y362" s="1" t="s">
         <v>27</v>
       </c>
@@ -40535,7 +40659,9 @@
       <c r="W363" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="X363" s="1"/>
+      <c r="X363" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y363" s="1" t="s">
         <v>1541</v>
       </c>
@@ -40628,7 +40754,9 @@
       <c r="W364" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="X364" s="1"/>
+      <c r="X364" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y364" s="1" t="s">
         <v>27</v>
       </c>
@@ -40721,7 +40849,9 @@
       <c r="W365" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X365" s="1"/>
+      <c r="X365" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y365" s="1" t="s">
         <v>27</v>
       </c>
@@ -40814,7 +40944,9 @@
       <c r="W366" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="X366" s="1"/>
+      <c r="X366" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y366" s="1" t="s">
         <v>1541</v>
       </c>
@@ -40907,7 +41039,9 @@
       <c r="W367" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X367" s="1"/>
+      <c r="X367" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y367" s="1" t="s">
         <v>266</v>
       </c>
@@ -41000,7 +41134,9 @@
       <c r="W368" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X368" s="1"/>
+      <c r="X368" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y368" s="1" t="s">
         <v>27</v>
       </c>
@@ -41093,7 +41229,9 @@
       <c r="W369" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X369" s="1"/>
+      <c r="X369" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y369" s="1" t="s">
         <v>1541</v>
       </c>
@@ -41186,7 +41324,9 @@
       <c r="W370" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="X370" s="1"/>
+      <c r="X370" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y370" s="1" t="s">
         <v>1541</v>
       </c>
@@ -41279,7 +41419,9 @@
       <c r="W371" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="X371" s="1"/>
+      <c r="X371" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y371" s="1" t="s">
         <v>1541</v>
       </c>
@@ -41370,9 +41512,11 @@
         <v>27</v>
       </c>
       <c r="W372" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="X372" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="X372" s="1"/>
       <c r="Y372" s="1" t="s">
         <v>266</v>
       </c>
@@ -41465,7 +41609,9 @@
       <c r="W373" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X373" s="1"/>
+      <c r="X373" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y373" s="1" t="s">
         <v>266</v>
       </c>
@@ -41558,7 +41704,9 @@
       <c r="W374" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X374" s="1"/>
+      <c r="X374" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y374" s="1" t="s">
         <v>1541</v>
       </c>
@@ -41649,9 +41797,11 @@
         <v>27</v>
       </c>
       <c r="W375" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="X375" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="X375" s="1"/>
       <c r="Y375" s="1" t="s">
         <v>71</v>
       </c>
@@ -41744,7 +41894,9 @@
       <c r="W376" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="X376" s="1"/>
+      <c r="X376" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y376" s="1" t="s">
         <v>1541</v>
       </c>
@@ -41837,7 +41989,9 @@
       <c r="W377" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X377" s="1"/>
+      <c r="X377" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y377" s="1" t="s">
         <v>27</v>
       </c>
@@ -41928,9 +42082,11 @@
         <v>27</v>
       </c>
       <c r="W378" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="X378" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="X378" s="1"/>
       <c r="Y378" s="1" t="s">
         <v>266</v>
       </c>
@@ -42023,7 +42179,9 @@
       <c r="W379" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="X379" s="1"/>
+      <c r="X379" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y379" s="1" t="s">
         <v>1541</v>
       </c>
@@ -42116,7 +42274,9 @@
       <c r="W380" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X380" s="1"/>
+      <c r="X380" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y380" s="1" t="s">
         <v>266</v>
       </c>
@@ -42209,7 +42369,9 @@
       <c r="W381" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X381" s="1"/>
+      <c r="X381" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y381" s="1" t="s">
         <v>27</v>
       </c>
@@ -42302,7 +42464,9 @@
       <c r="W382" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="X382" s="1"/>
+      <c r="X382" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y382" s="1" t="s">
         <v>1541</v>
       </c>
@@ -42395,7 +42559,9 @@
       <c r="W383" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X383" s="1"/>
+      <c r="X383" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y383" s="1" t="s">
         <v>1541</v>
       </c>
@@ -42488,7 +42654,9 @@
       <c r="W384" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="X384" s="1"/>
+      <c r="X384" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y384" s="1" t="s">
         <v>1541</v>
       </c>
@@ -42581,7 +42749,9 @@
       <c r="W385" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X385" s="1"/>
+      <c r="X385" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y385" s="1" t="s">
         <v>1541</v>
       </c>
@@ -42672,9 +42842,11 @@
         <v>27</v>
       </c>
       <c r="W386" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="X386" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="X386" s="1"/>
       <c r="Y386" s="1" t="s">
         <v>266</v>
       </c>
@@ -42767,7 +42939,9 @@
       <c r="W387" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="X387" s="1"/>
+      <c r="X387" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y387" s="1" t="s">
         <v>1541</v>
       </c>
@@ -42860,7 +43034,9 @@
       <c r="W388" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X388" s="1"/>
+      <c r="X388" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y388" s="1" t="s">
         <v>27</v>
       </c>
@@ -42953,7 +43129,9 @@
       <c r="W389" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="X389" s="1"/>
+      <c r="X389" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y389" s="1" t="s">
         <v>1541</v>
       </c>
@@ -43044,9 +43222,11 @@
         <v>27</v>
       </c>
       <c r="W390" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="X390" s="1" t="s">
         <v>1521</v>
       </c>
-      <c r="X390" s="1"/>
       <c r="Y390" s="1" t="s">
         <v>27</v>
       </c>
@@ -43137,9 +43317,11 @@
         <v>27</v>
       </c>
       <c r="W391" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="X391" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="X391" s="1"/>
       <c r="Y391" s="1" t="s">
         <v>266</v>
       </c>
@@ -43232,7 +43414,9 @@
       <c r="W392" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="X392" s="1"/>
+      <c r="X392" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y392" s="1" t="s">
         <v>1541</v>
       </c>
@@ -43325,7 +43509,9 @@
       <c r="W393" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X393" s="1"/>
+      <c r="X393" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y393" s="1" t="s">
         <v>27</v>
       </c>
@@ -43418,7 +43604,9 @@
       <c r="W394" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="X394" s="1"/>
+      <c r="X394" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y394" s="1" t="s">
         <v>1541</v>
       </c>
@@ -43511,7 +43699,9 @@
       <c r="W395" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X395" s="1"/>
+      <c r="X395" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y395" s="1" t="s">
         <v>27</v>
       </c>
@@ -43604,7 +43794,9 @@
       <c r="W396" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="X396" s="1"/>
+      <c r="X396" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y396" s="1" t="s">
         <v>27</v>
       </c>
@@ -43697,7 +43889,9 @@
       <c r="W397" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X397" s="1"/>
+      <c r="X397" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y397" s="1" t="s">
         <v>266</v>
       </c>
@@ -43790,7 +43984,9 @@
       <c r="W398" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="X398" s="1"/>
+      <c r="X398" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y398" s="1" t="s">
         <v>27</v>
       </c>
@@ -43883,7 +44079,9 @@
       <c r="W399" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="X399" s="1"/>
+      <c r="X399" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y399" s="1" t="s">
         <v>1541</v>
       </c>
@@ -43976,7 +44174,9 @@
       <c r="W400" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X400" s="1"/>
+      <c r="X400" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y400" s="1" t="s">
         <v>1541</v>
       </c>
@@ -44069,7 +44269,9 @@
       <c r="W401" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X401" s="1"/>
+      <c r="X401" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y401" s="1" t="s">
         <v>266</v>
       </c>
@@ -44160,9 +44362,11 @@
         <v>27</v>
       </c>
       <c r="W402" s="1" t="s">
+        <v>1750</v>
+      </c>
+      <c r="X402" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="X402" s="1"/>
       <c r="Y402" s="1" t="s">
         <v>1615</v>
       </c>
@@ -44253,9 +44457,11 @@
         <v>27</v>
       </c>
       <c r="W403" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="X403" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="X403" s="1"/>
       <c r="Y403" s="1" t="s">
         <v>266</v>
       </c>
@@ -44346,9 +44552,11 @@
         <v>27</v>
       </c>
       <c r="W404" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="X404" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="X404" s="1"/>
       <c r="Y404" s="1" t="s">
         <v>27</v>
       </c>
@@ -44371,96 +44579,98 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="405" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A405" s="1" t="s">
+    <row r="405" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A405" s="5" t="s">
         <v>1229</v>
       </c>
-      <c r="B405" s="1" t="s">
+      <c r="B405" s="5" t="s">
         <v>1239</v>
       </c>
-      <c r="C405" s="1" t="s">
+      <c r="C405" s="5" t="s">
         <v>1240</v>
       </c>
-      <c r="D405" s="1" t="s">
+      <c r="D405" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="E405" s="1" t="s">
+      <c r="E405" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H405" s="1" t="s">
+      <c r="F405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H405" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N405" s="1" t="s">
+      <c r="I405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N405" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="O405" s="1" t="s">
+      <c r="O405" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="P405" s="1" t="s">
+      <c r="P405" s="5" t="s">
         <v>1258</v>
       </c>
-      <c r="Q405" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R405" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S405" s="1" t="s">
+      <c r="Q405" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R405" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S405" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="T405" s="1" t="s">
+      <c r="T405" s="5" t="s">
         <v>1545</v>
       </c>
-      <c r="U405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W405" s="1" t="s">
+      <c r="U405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="W405" s="5" t="s">
         <v>1259</v>
       </c>
-      <c r="X405" s="1"/>
-      <c r="Y405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z405" s="1" t="s">
+      <c r="X405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z405" s="5" t="s">
         <v>1536</v>
       </c>
-      <c r="AA405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB405" s="1" t="s">
+      <c r="AA405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB405" s="5" t="s">
         <v>1580</v>
       </c>
-      <c r="AC405" s="1" t="s">
+      <c r="AC405" s="5" t="s">
         <v>1563</v>
       </c>
-      <c r="AD405" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE405" s="1" t="s">
+      <c r="AD405" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE405" s="5" t="s">
         <v>1260</v>
       </c>
     </row>
@@ -44534,7 +44744,9 @@
       <c r="W406" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X406" s="1"/>
+      <c r="X406" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y406" s="1" t="s">
         <v>266</v>
       </c>
@@ -44627,7 +44839,9 @@
       <c r="W407" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="X407" s="1"/>
+      <c r="X407" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y407" s="1" t="s">
         <v>1541</v>
       </c>
@@ -44718,9 +44932,11 @@
         <v>27</v>
       </c>
       <c r="W408" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="X408" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="X408" s="1"/>
       <c r="Y408" s="1" t="s">
         <v>1541</v>
       </c>
@@ -44813,7 +45029,9 @@
       <c r="W409" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="X409" s="1"/>
+      <c r="X409" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y409" s="1" t="s">
         <v>1541</v>
       </c>
@@ -44906,7 +45124,9 @@
       <c r="W410" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="X410" s="1"/>
+      <c r="X410" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y410" s="1" t="s">
         <v>27</v>
       </c>
@@ -44997,9 +45217,11 @@
         <v>27</v>
       </c>
       <c r="W411" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="X411" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="X411" s="1"/>
       <c r="Y411" s="1" t="s">
         <v>27</v>
       </c>
@@ -45090,9 +45312,11 @@
         <v>27</v>
       </c>
       <c r="W412" s="1" t="s">
+        <v>1756</v>
+      </c>
+      <c r="X412" s="1" t="s">
         <v>1522</v>
       </c>
-      <c r="X412" s="1"/>
       <c r="Y412" s="1" t="s">
         <v>1541</v>
       </c>
@@ -45185,7 +45409,9 @@
       <c r="W413" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="X413" s="1"/>
+      <c r="X413" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y413" s="1" t="s">
         <v>266</v>
       </c>
@@ -45276,9 +45502,11 @@
         <v>27</v>
       </c>
       <c r="W414" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="X414" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="X414" s="1"/>
       <c r="Y414" s="1" t="s">
         <v>27</v>
       </c>
@@ -45315,7 +45543,7 @@
         <v>26</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>124</v>
+        <v>1283</v>
       </c>
       <c r="F415" s="1" t="s">
         <v>27</v>
@@ -45324,10 +45552,10 @@
         <v>27</v>
       </c>
       <c r="H415" s="1" t="s">
-        <v>1286</v>
+        <v>39</v>
       </c>
       <c r="I415" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J415" s="1" t="s">
         <v>27</v>
@@ -45336,31 +45564,31 @@
         <v>27</v>
       </c>
       <c r="L415" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M415" s="1">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="M415" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N415" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O415" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P415" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q415" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R415" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S415" s="1" t="s">
-        <v>27</v>
+        <v>330</v>
       </c>
       <c r="T415" s="1" t="s">
-        <v>27</v>
+        <v>1545</v>
       </c>
       <c r="U415" s="1" t="s">
         <v>27</v>
@@ -45369,14 +45597,16 @@
         <v>27</v>
       </c>
       <c r="W415" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="X415" s="1"/>
+        <v>1736</v>
+      </c>
+      <c r="X415" s="1" t="s">
+        <v>1284</v>
+      </c>
       <c r="Y415" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z415" s="1" t="s">
-        <v>1536</v>
+        <v>27</v>
       </c>
       <c r="AA415" s="1" t="s">
         <v>27</v>
@@ -45391,7 +45621,7 @@
         <v>27</v>
       </c>
       <c r="AE415" s="1" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="416" spans="1:31" x14ac:dyDescent="0.45">
@@ -45417,10 +45647,10 @@
         <v>27</v>
       </c>
       <c r="H416" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="I416" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J416" s="1" t="s">
         <v>27</v>
@@ -45462,11 +45692,13 @@
         <v>27</v>
       </c>
       <c r="W416" s="1" t="s">
-        <v>1477</v>
-      </c>
-      <c r="X416" s="1"/>
+        <v>310</v>
+      </c>
+      <c r="X416" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y416" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z416" s="1" t="s">
         <v>1536</v>
@@ -45501,7 +45733,7 @@
         <v>26</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>1289</v>
+        <v>124</v>
       </c>
       <c r="F417" s="1" t="s">
         <v>27</v>
@@ -45510,10 +45742,10 @@
         <v>27</v>
       </c>
       <c r="H417" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="I417" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="J417" s="1" t="s">
         <v>27</v>
@@ -45522,31 +45754,31 @@
         <v>27</v>
       </c>
       <c r="L417" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M417" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M417" s="1">
+        <v>1</v>
       </c>
       <c r="N417" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O417" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P417" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Q417" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R417" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S417" s="1" t="s">
-        <v>207</v>
+        <v>27</v>
       </c>
       <c r="T417" s="1" t="s">
-        <v>1545</v>
+        <v>27</v>
       </c>
       <c r="U417" s="1" t="s">
         <v>27</v>
@@ -45555,11 +45787,13 @@
         <v>27</v>
       </c>
       <c r="W417" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="X417" s="1"/>
+        <v>1477</v>
+      </c>
+      <c r="X417" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y417" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z417" s="1" t="s">
         <v>1536</v>
@@ -45574,27 +45808,27 @@
         <v>1543</v>
       </c>
       <c r="AD417" s="1" t="s">
-        <v>1291</v>
+        <v>27</v>
       </c>
       <c r="AE417" s="1" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="418" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A418" s="1" t="s">
-        <v>1293</v>
+        <v>1229</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1294</v>
+        <v>1281</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
       <c r="F418" s="1" t="s">
         <v>27</v>
@@ -45603,7 +45837,7 @@
         <v>27</v>
       </c>
       <c r="H418" s="1" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="I418" s="1" t="s">
         <v>126</v>
@@ -45636,10 +45870,10 @@
         <v>27</v>
       </c>
       <c r="S418" s="1" t="s">
-        <v>27</v>
+        <v>207</v>
       </c>
       <c r="T418" s="1" t="s">
-        <v>27</v>
+        <v>1545</v>
       </c>
       <c r="U418" s="1" t="s">
         <v>27</v>
@@ -45648,11 +45882,13 @@
         <v>27</v>
       </c>
       <c r="W418" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X418" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="X418" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y418" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z418" s="1" t="s">
         <v>1536</v>
@@ -45661,16 +45897,16 @@
         <v>27</v>
       </c>
       <c r="AB418" s="1" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="AC418" s="1" t="s">
         <v>1543</v>
       </c>
       <c r="AD418" s="1" t="s">
-        <v>27</v>
+        <v>1291</v>
       </c>
       <c r="AE418" s="1" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="419" spans="1:31" x14ac:dyDescent="0.45">
@@ -45687,7 +45923,7 @@
         <v>172</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="F419" s="1" t="s">
         <v>27</v>
@@ -45696,10 +45932,10 @@
         <v>27</v>
       </c>
       <c r="H419" s="1" t="s">
-        <v>814</v>
+        <v>1297</v>
       </c>
       <c r="I419" s="1" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="J419" s="1" t="s">
         <v>27</v>
@@ -45708,31 +45944,31 @@
         <v>27</v>
       </c>
       <c r="L419" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M419" s="1">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="M419" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N419" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O419" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P419" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q419" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R419" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S419" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="T419" s="1" t="s">
-        <v>1545</v>
+        <v>27</v>
       </c>
       <c r="U419" s="1" t="s">
         <v>27</v>
@@ -45741,11 +45977,13 @@
         <v>27</v>
       </c>
       <c r="W419" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X419" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X419" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y419" s="1" t="s">
-        <v>1547</v>
+        <v>27</v>
       </c>
       <c r="Z419" s="1" t="s">
         <v>1536</v>
@@ -45754,7 +45992,7 @@
         <v>27</v>
       </c>
       <c r="AB419" s="1" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="AC419" s="1" t="s">
         <v>1543</v>
@@ -45763,7 +46001,7 @@
         <v>27</v>
       </c>
       <c r="AE419" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="420" spans="1:31" x14ac:dyDescent="0.45">
@@ -45834,11 +46072,13 @@
         <v>27</v>
       </c>
       <c r="W420" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="X420" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X420" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y420" s="1" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="Z420" s="1" t="s">
         <v>1536</v>
@@ -45864,16 +46104,16 @@
         <v>1293</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>1301</v>
+        <v>1294</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>1302</v>
+        <v>1295</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="F421" s="1" t="s">
         <v>27</v>
@@ -45882,10 +46122,10 @@
         <v>27</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>1304</v>
+        <v>814</v>
       </c>
       <c r="I421" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J421" s="1" t="s">
         <v>27</v>
@@ -45915,10 +46155,10 @@
         <v>31</v>
       </c>
       <c r="S421" s="1" t="s">
-        <v>254</v>
+        <v>128</v>
       </c>
       <c r="T421" s="1" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="U421" s="1" t="s">
         <v>27</v>
@@ -45927,11 +46167,13 @@
         <v>27</v>
       </c>
       <c r="W421" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X421" s="1"/>
+        <v>1365</v>
+      </c>
+      <c r="X421" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y421" s="1" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="Z421" s="1" t="s">
         <v>1536</v>
@@ -45946,10 +46188,10 @@
         <v>1543</v>
       </c>
       <c r="AD421" s="1" t="s">
-        <v>1305</v>
+        <v>27</v>
       </c>
       <c r="AE421" s="1" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="422" spans="1:31" x14ac:dyDescent="0.45">
@@ -45969,13 +46211,13 @@
         <v>1303</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>837</v>
+        <v>27</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>126</v>
@@ -45999,7 +46241,7 @@
         <v>29</v>
       </c>
       <c r="P422" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q422" s="1" t="s">
         <v>31</v>
@@ -46008,10 +46250,10 @@
         <v>31</v>
       </c>
       <c r="S422" s="1" t="s">
-        <v>1308</v>
+        <v>254</v>
       </c>
       <c r="T422" s="1" t="s">
-        <v>1581</v>
+        <v>1540</v>
       </c>
       <c r="U422" s="1" t="s">
         <v>27</v>
@@ -46020,11 +46262,13 @@
         <v>27</v>
       </c>
       <c r="W422" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X422" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X422" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y422" s="1" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="Z422" s="1" t="s">
         <v>1536</v>
@@ -46033,13 +46277,13 @@
         <v>27</v>
       </c>
       <c r="AB422" s="1" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="AC422" s="1" t="s">
         <v>1543</v>
       </c>
       <c r="AD422" s="1" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="AE422" s="1" t="s">
         <v>1306</v>
@@ -46050,25 +46294,25 @@
         <v>1293</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>1310</v>
+        <v>1301</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>1311</v>
+        <v>1302</v>
       </c>
       <c r="D423" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>27</v>
+        <v>837</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>1313</v>
+        <v>1307</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>126</v>
@@ -46080,19 +46324,19 @@
         <v>27</v>
       </c>
       <c r="L423" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M423" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M423" s="1">
+        <v>1</v>
       </c>
       <c r="N423" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="O423" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="P423" s="1" t="s">
-        <v>1314</v>
+        <v>30</v>
       </c>
       <c r="Q423" s="1" t="s">
         <v>31</v>
@@ -46101,23 +46345,25 @@
         <v>31</v>
       </c>
       <c r="S423" s="1" t="s">
-        <v>1315</v>
+        <v>1308</v>
       </c>
       <c r="T423" s="1" t="s">
-        <v>1545</v>
+        <v>1581</v>
       </c>
       <c r="U423" s="1" t="s">
-        <v>1316</v>
+        <v>27</v>
       </c>
       <c r="V423" s="1" t="s">
         <v>27</v>
       </c>
       <c r="W423" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="X423" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X423" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y423" s="1" t="s">
-        <v>266</v>
+        <v>1541</v>
       </c>
       <c r="Z423" s="1" t="s">
         <v>1536</v>
@@ -46132,10 +46378,10 @@
         <v>1543</v>
       </c>
       <c r="AD423" s="1" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
       <c r="AE423" s="1" t="s">
-        <v>1318</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="424" spans="1:31" x14ac:dyDescent="0.45">
@@ -46143,16 +46389,16 @@
         <v>1293</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>1533</v>
+        <v>1310</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>674</v>
+        <v>1312</v>
       </c>
       <c r="F424" s="1" t="s">
         <v>27</v>
@@ -46161,10 +46407,10 @@
         <v>27</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
       <c r="I424" s="1" t="s">
-        <v>1570</v>
+        <v>126</v>
       </c>
       <c r="J424" s="1" t="s">
         <v>27</v>
@@ -46173,19 +46419,19 @@
         <v>27</v>
       </c>
       <c r="L424" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M424" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N424" s="1" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="O424" s="1" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="P424" s="1" t="s">
-        <v>30</v>
+        <v>1314</v>
       </c>
       <c r="Q424" s="1" t="s">
         <v>31</v>
@@ -46194,23 +46440,25 @@
         <v>31</v>
       </c>
       <c r="S424" s="1" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="T424" s="1" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="U424" s="1" t="s">
-        <v>27</v>
+        <v>1316</v>
       </c>
       <c r="V424" s="1" t="s">
         <v>27</v>
       </c>
       <c r="W424" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X424" s="1"/>
+        <v>551</v>
+      </c>
+      <c r="X424" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y424" s="1" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="Z424" s="1" t="s">
         <v>1536</v>
@@ -46225,10 +46473,10 @@
         <v>1543</v>
       </c>
       <c r="AD424" s="1" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="AE424" s="1" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="425" spans="1:31" x14ac:dyDescent="0.45">
@@ -46254,7 +46502,7 @@
         <v>27</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>1570</v>
@@ -46268,8 +46516,8 @@
       <c r="L425" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M425" s="1">
-        <v>1</v>
+      <c r="M425" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N425" s="1" t="s">
         <v>29</v>
@@ -46278,7 +46526,7 @@
         <v>29</v>
       </c>
       <c r="P425" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q425" s="1" t="s">
         <v>31</v>
@@ -46287,10 +46535,10 @@
         <v>31</v>
       </c>
       <c r="S425" s="1" t="s">
-        <v>612</v>
+        <v>1321</v>
       </c>
       <c r="T425" s="1" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="U425" s="1" t="s">
         <v>27</v>
@@ -46299,11 +46547,13 @@
         <v>27</v>
       </c>
       <c r="W425" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X425" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X425" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y425" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z425" s="1" t="s">
         <v>1536</v>
@@ -46312,16 +46562,16 @@
         <v>27</v>
       </c>
       <c r="AB425" s="1" t="s">
-        <v>27</v>
+        <v>1537</v>
       </c>
       <c r="AC425" s="1" t="s">
-        <v>27</v>
+        <v>1543</v>
       </c>
       <c r="AD425" s="1" t="s">
-        <v>27</v>
+        <v>1322</v>
       </c>
       <c r="AE425" s="1" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="426" spans="1:31" x14ac:dyDescent="0.45">
@@ -46392,11 +46642,13 @@
         <v>27</v>
       </c>
       <c r="W426" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X426" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X426" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y426" s="1" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="Z426" s="1" t="s">
         <v>1536</v>
@@ -46422,16 +46674,16 @@
         <v>1293</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>1326</v>
+        <v>1533</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="D427" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>1121</v>
+        <v>674</v>
       </c>
       <c r="F427" s="1" t="s">
         <v>27</v>
@@ -46440,10 +46692,10 @@
         <v>27</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>61</v>
+        <v>1324</v>
       </c>
       <c r="I427" s="1" t="s">
-        <v>27</v>
+        <v>1570</v>
       </c>
       <c r="J427" s="1" t="s">
         <v>27</v>
@@ -46458,13 +46710,13 @@
         <v>1</v>
       </c>
       <c r="N427" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="O427" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="P427" s="1" t="s">
-        <v>675</v>
+        <v>40</v>
       </c>
       <c r="Q427" s="1" t="s">
         <v>31</v>
@@ -46473,7 +46725,7 @@
         <v>31</v>
       </c>
       <c r="S427" s="1" t="s">
-        <v>1328</v>
+        <v>612</v>
       </c>
       <c r="T427" s="1" t="s">
         <v>1545</v>
@@ -46485,11 +46737,13 @@
         <v>27</v>
       </c>
       <c r="W427" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="X427" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X427" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y427" s="1" t="s">
-        <v>266</v>
+        <v>1547</v>
       </c>
       <c r="Z427" s="1" t="s">
         <v>1536</v>
@@ -46498,16 +46752,16 @@
         <v>27</v>
       </c>
       <c r="AB427" s="1" t="s">
-        <v>1537</v>
+        <v>27</v>
       </c>
       <c r="AC427" s="1" t="s">
-        <v>1543</v>
+        <v>27</v>
       </c>
       <c r="AD427" s="1" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="AE427" s="1" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="428" spans="1:31" x14ac:dyDescent="0.45">
@@ -46515,16 +46769,16 @@
         <v>1293</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>1332</v>
+        <v>1121</v>
       </c>
       <c r="F428" s="1" t="s">
         <v>27</v>
@@ -46533,7 +46787,7 @@
         <v>27</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>27</v>
@@ -46547,17 +46801,17 @@
       <c r="L428" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M428" s="1" t="s">
-        <v>625</v>
+      <c r="M428" s="1">
+        <v>1</v>
       </c>
       <c r="N428" s="1" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="O428" s="1" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="P428" s="1" t="s">
-        <v>1333</v>
+        <v>675</v>
       </c>
       <c r="Q428" s="1" t="s">
         <v>31</v>
@@ -46566,7 +46820,7 @@
         <v>31</v>
       </c>
       <c r="S428" s="1" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="T428" s="1" t="s">
         <v>1545</v>
@@ -46578,9 +46832,11 @@
         <v>27</v>
       </c>
       <c r="W428" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="X428" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="X428" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y428" s="1" t="s">
         <v>266</v>
       </c>
@@ -46597,10 +46853,10 @@
         <v>1543</v>
       </c>
       <c r="AD428" s="1" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
       <c r="AE428" s="1" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="429" spans="1:31" x14ac:dyDescent="0.45">
@@ -46671,11 +46927,13 @@
         <v>27</v>
       </c>
       <c r="W429" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X429" s="1"/>
+        <v>551</v>
+      </c>
+      <c r="X429" s="1" t="s">
+        <v>810</v>
+      </c>
       <c r="Y429" s="1" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="Z429" s="1" t="s">
         <v>1536</v>
@@ -46719,7 +46977,7 @@
         <v>27</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="I430" s="1" t="s">
         <v>27</v>
@@ -46733,17 +46991,17 @@
       <c r="L430" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M430" s="1">
-        <v>1</v>
+      <c r="M430" s="1" t="s">
+        <v>625</v>
       </c>
       <c r="N430" s="1" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="O430" s="1" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="P430" s="1" t="s">
-        <v>40</v>
+        <v>1333</v>
       </c>
       <c r="Q430" s="1" t="s">
         <v>31</v>
@@ -46752,10 +47010,10 @@
         <v>31</v>
       </c>
       <c r="S430" s="1" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="T430" s="1" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="U430" s="1" t="s">
         <v>27</v>
@@ -46764,20 +47022,22 @@
         <v>27</v>
       </c>
       <c r="W430" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="X430" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X430" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y430" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z430" s="1" t="s">
-        <v>27</v>
+        <v>1536</v>
       </c>
       <c r="AA430" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB430" s="1" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="AC430" s="1" t="s">
         <v>1543</v>
@@ -46857,14 +47117,16 @@
         <v>27</v>
       </c>
       <c r="W431" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X431" s="1"/>
+        <v>786</v>
+      </c>
+      <c r="X431" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y431" s="1" t="s">
-        <v>1547</v>
+        <v>27</v>
       </c>
       <c r="Z431" s="1" t="s">
-        <v>1536</v>
+        <v>27</v>
       </c>
       <c r="AA431" s="1" t="s">
         <v>27</v>
@@ -46896,7 +47158,7 @@
         <v>26</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="F432" s="1" t="s">
         <v>27</v>
@@ -46938,10 +47200,10 @@
         <v>31</v>
       </c>
       <c r="S432" s="1" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="T432" s="1" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="U432" s="1" t="s">
         <v>27</v>
@@ -46950,29 +47212,31 @@
         <v>27</v>
       </c>
       <c r="W432" s="1" t="s">
-        <v>1339</v>
-      </c>
-      <c r="X432" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X432" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y432" s="1" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="Z432" s="1" t="s">
-        <v>27</v>
+        <v>1536</v>
       </c>
       <c r="AA432" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB432" s="1" t="s">
-        <v>27</v>
+        <v>1544</v>
       </c>
       <c r="AC432" s="1" t="s">
-        <v>27</v>
+        <v>1543</v>
       </c>
       <c r="AD432" s="1" t="s">
-        <v>27</v>
+        <v>214</v>
       </c>
       <c r="AE432" s="1" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="433" spans="1:31" x14ac:dyDescent="0.45">
@@ -46980,16 +47244,16 @@
         <v>1293</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>1532</v>
+        <v>1330</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>1341</v>
+        <v>1331</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="F433" s="1" t="s">
         <v>27</v>
@@ -46998,10 +47262,10 @@
         <v>27</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>1343</v>
+        <v>147</v>
       </c>
       <c r="I433" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J433" s="1" t="s">
         <v>27</v>
@@ -47022,7 +47286,7 @@
         <v>29</v>
       </c>
       <c r="P433" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q433" s="1" t="s">
         <v>31</v>
@@ -47031,10 +47295,10 @@
         <v>31</v>
       </c>
       <c r="S433" s="1" t="s">
-        <v>27</v>
+        <v>1338</v>
       </c>
       <c r="T433" s="1" t="s">
-        <v>27</v>
+        <v>1545</v>
       </c>
       <c r="U433" s="1" t="s">
         <v>27</v>
@@ -47043,29 +47307,31 @@
         <v>27</v>
       </c>
       <c r="W433" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X433" s="1"/>
+        <v>1391</v>
+      </c>
+      <c r="X433" s="1" t="s">
+        <v>1339</v>
+      </c>
       <c r="Y433" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z433" s="1" t="s">
-        <v>1536</v>
+        <v>27</v>
       </c>
       <c r="AA433" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB433" s="1" t="s">
-        <v>1537</v>
+        <v>27</v>
       </c>
       <c r="AC433" s="1" t="s">
-        <v>1543</v>
+        <v>27</v>
       </c>
       <c r="AD433" s="1" t="s">
-        <v>1344</v>
+        <v>27</v>
       </c>
       <c r="AE433" s="1" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="434" spans="1:31" x14ac:dyDescent="0.45">
@@ -47073,16 +47339,16 @@
         <v>1293</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>1346</v>
+        <v>1532</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="F434" s="1" t="s">
         <v>27</v>
@@ -47091,56 +47357,58 @@
         <v>27</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>1111</v>
+        <v>1343</v>
       </c>
       <c r="I434" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J434" s="1" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="K434" s="1" t="s">
-        <v>1147</v>
+        <v>27</v>
       </c>
       <c r="L434" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M434" s="1" t="s">
-        <v>27</v>
+      <c r="M434" s="1">
+        <v>1</v>
       </c>
       <c r="N434" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="O434" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="P434" s="1" t="s">
-        <v>465</v>
+        <v>30</v>
       </c>
       <c r="Q434" s="1" t="s">
-        <v>201</v>
+        <v>31</v>
       </c>
       <c r="R434" s="1" t="s">
-        <v>201</v>
+        <v>31</v>
       </c>
       <c r="S434" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="T434" s="1" t="s">
-        <v>1545</v>
+        <v>27</v>
       </c>
       <c r="U434" s="1" t="s">
-        <v>1349</v>
+        <v>27</v>
       </c>
       <c r="V434" s="1" t="s">
         <v>27</v>
       </c>
       <c r="W434" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X434" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X434" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y434" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z434" s="1" t="s">
         <v>1536</v>
@@ -47149,16 +47417,16 @@
         <v>27</v>
       </c>
       <c r="AB434" s="1" t="s">
-        <v>27</v>
+        <v>1537</v>
       </c>
       <c r="AC434" s="1" t="s">
-        <v>27</v>
+        <v>1543</v>
       </c>
       <c r="AD434" s="1" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="AE434" s="1" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="435" spans="1:31" x14ac:dyDescent="0.45">
@@ -47229,14 +47497,16 @@
         <v>27</v>
       </c>
       <c r="W435" s="1" t="s">
-        <v>1391</v>
-      </c>
-      <c r="X435" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X435" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y435" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z435" s="1" t="s">
-        <v>27</v>
+        <v>1536</v>
       </c>
       <c r="AA435" s="1" t="s">
         <v>27</v>
@@ -47268,7 +47538,7 @@
         <v>172</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>1688</v>
+        <v>1348</v>
       </c>
       <c r="F436" s="1" t="s">
         <v>27</v>
@@ -47289,28 +47559,28 @@
         <v>1147</v>
       </c>
       <c r="L436" s="1" t="s">
-        <v>1352</v>
+        <v>28</v>
       </c>
       <c r="M436" s="1" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="N436" s="1" t="s">
-        <v>1271</v>
+        <v>130</v>
       </c>
       <c r="O436" s="1" t="s">
-        <v>1735</v>
+        <v>130</v>
       </c>
       <c r="P436" s="1" t="s">
-        <v>1353</v>
+        <v>465</v>
       </c>
       <c r="Q436" s="1" t="s">
-        <v>1731</v>
+        <v>201</v>
       </c>
       <c r="R436" s="1" t="s">
-        <v>1730</v>
+        <v>201</v>
       </c>
       <c r="S436" s="1" t="s">
-        <v>1686</v>
+        <v>128</v>
       </c>
       <c r="T436" s="1" t="s">
         <v>1545</v>
@@ -47322,29 +47592,31 @@
         <v>27</v>
       </c>
       <c r="W436" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="X436" s="1"/>
+        <v>1391</v>
+      </c>
+      <c r="X436" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y436" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z436" s="1" t="s">
-        <v>1536</v>
+        <v>27</v>
       </c>
       <c r="AA436" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB436" s="1" t="s">
-        <v>1537</v>
+        <v>27</v>
       </c>
       <c r="AC436" s="1" t="s">
-        <v>1543</v>
+        <v>27</v>
       </c>
       <c r="AD436" s="1" t="s">
         <v>1350</v>
       </c>
       <c r="AE436" s="1" t="s">
-        <v>1687</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="437" spans="1:31" x14ac:dyDescent="0.45">
@@ -47415,9 +47687,11 @@
         <v>27</v>
       </c>
       <c r="W437" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X437" s="1"/>
+        <v>226</v>
+      </c>
+      <c r="X437" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y437" s="1" t="s">
         <v>27</v>
       </c>
@@ -47454,7 +47728,7 @@
         <v>172</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>925</v>
+        <v>1688</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>27</v>
@@ -47463,16 +47737,16 @@
         <v>27</v>
       </c>
       <c r="H438" s="1" t="s">
-        <v>61</v>
+        <v>1111</v>
       </c>
       <c r="I438" s="1" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="J438" s="1" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="K438" s="1" t="s">
-        <v>27</v>
+        <v>1147</v>
       </c>
       <c r="L438" s="1" t="s">
         <v>1352</v>
@@ -47490,29 +47764,31 @@
         <v>1353</v>
       </c>
       <c r="Q438" s="1" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="R438" s="1" t="s">
         <v>1730</v>
       </c>
       <c r="S438" s="1" t="s">
-        <v>944</v>
+        <v>1686</v>
       </c>
       <c r="T438" s="1" t="s">
         <v>1545</v>
       </c>
       <c r="U438" s="1" t="s">
-        <v>27</v>
+        <v>1349</v>
       </c>
       <c r="V438" s="1" t="s">
         <v>27</v>
       </c>
       <c r="W438" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="X438" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X438" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y438" s="1" t="s">
-        <v>266</v>
+        <v>27</v>
       </c>
       <c r="Z438" s="1" t="s">
         <v>1536</v>
@@ -47527,10 +47803,10 @@
         <v>1543</v>
       </c>
       <c r="AD438" s="1" t="s">
-        <v>27</v>
+        <v>1350</v>
       </c>
       <c r="AE438" s="1" t="s">
-        <v>1354</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="439" spans="1:31" x14ac:dyDescent="0.45">
@@ -47601,11 +47877,13 @@
         <v>27</v>
       </c>
       <c r="W439" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X439" s="1"/>
+        <v>551</v>
+      </c>
+      <c r="X439" s="1" t="s">
+        <v>810</v>
+      </c>
       <c r="Y439" s="1" t="s">
-        <v>1541</v>
+        <v>266</v>
       </c>
       <c r="Z439" s="1" t="s">
         <v>1536</v>
@@ -47631,74 +47909,76 @@
         <v>1293</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>1355</v>
+        <v>1346</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>1356</v>
+        <v>1347</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>37</v>
+        <v>172</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>1357</v>
+        <v>925</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>1358</v>
+        <v>27</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>1359</v>
+        <v>27</v>
       </c>
       <c r="H440" s="1" t="s">
-        <v>1689</v>
+        <v>61</v>
       </c>
       <c r="I440" s="1" t="s">
-        <v>1570</v>
+        <v>27</v>
       </c>
       <c r="J440" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K440" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L440" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="M440" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="K440" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L440" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M440" s="1">
-        <v>1</v>
-      </c>
       <c r="N440" s="1" t="s">
-        <v>62</v>
+        <v>1271</v>
       </c>
       <c r="O440" s="1" t="s">
-        <v>62</v>
+        <v>1735</v>
       </c>
       <c r="P440" s="1" t="s">
-        <v>30</v>
+        <v>1353</v>
       </c>
       <c r="Q440" s="1" t="s">
-        <v>1360</v>
+        <v>1728</v>
       </c>
       <c r="R440" s="1" t="s">
         <v>1730</v>
       </c>
       <c r="S440" s="1" t="s">
-        <v>1690</v>
+        <v>944</v>
       </c>
       <c r="T440" s="1" t="s">
         <v>1545</v>
       </c>
       <c r="U440" s="1" t="s">
-        <v>1691</v>
+        <v>27</v>
       </c>
       <c r="V440" s="1" t="s">
         <v>27</v>
       </c>
       <c r="W440" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="X440" s="1"/>
+        <v>1097</v>
+      </c>
+      <c r="X440" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y440" s="1" t="s">
-        <v>266</v>
+        <v>1541</v>
       </c>
       <c r="Z440" s="1" t="s">
         <v>1536</v>
@@ -47710,13 +47990,13 @@
         <v>1537</v>
       </c>
       <c r="AC440" s="1" t="s">
-        <v>1563</v>
+        <v>1543</v>
       </c>
       <c r="AD440" s="1" t="s">
-        <v>1362</v>
+        <v>27</v>
       </c>
       <c r="AE440" s="1" t="s">
-        <v>1363</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="441" spans="1:31" x14ac:dyDescent="0.45">
@@ -47736,19 +48016,19 @@
         <v>1357</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>27</v>
+        <v>1358</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>27</v>
+        <v>1359</v>
       </c>
       <c r="H441" s="1" t="s">
-        <v>1364</v>
+        <v>1689</v>
       </c>
       <c r="I441" s="1" t="s">
-        <v>107</v>
+        <v>1570</v>
       </c>
       <c r="J441" s="1" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="K441" s="1" t="s">
         <v>27</v>
@@ -47760,38 +48040,40 @@
         <v>1</v>
       </c>
       <c r="N441" s="1" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="O441" s="1" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="P441" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q441" s="1" t="s">
-        <v>31</v>
+        <v>1360</v>
       </c>
       <c r="R441" s="1" t="s">
-        <v>31</v>
+        <v>1730</v>
       </c>
       <c r="S441" s="1" t="s">
-        <v>128</v>
+        <v>1690</v>
       </c>
       <c r="T441" s="1" t="s">
         <v>1545</v>
       </c>
       <c r="U441" s="1" t="s">
-        <v>27</v>
+        <v>1691</v>
       </c>
       <c r="V441" s="1" t="s">
         <v>27</v>
       </c>
       <c r="W441" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="X441" s="1"/>
+        <v>551</v>
+      </c>
+      <c r="X441" s="1" t="s">
+        <v>810</v>
+      </c>
       <c r="Y441" s="1" t="s">
-        <v>1541</v>
+        <v>266</v>
       </c>
       <c r="Z441" s="1" t="s">
         <v>1536</v>
@@ -47800,33 +48082,33 @@
         <v>27</v>
       </c>
       <c r="AB441" s="1" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="AC441" s="1" t="s">
         <v>1563</v>
       </c>
       <c r="AD441" s="1" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="AE441" s="1" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="442" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A442" s="1" t="s">
-        <v>1368</v>
+        <v>1293</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>1369</v>
+        <v>1355</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>1370</v>
+        <v>1356</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>1371</v>
+        <v>1357</v>
       </c>
       <c r="F442" s="1" t="s">
         <v>27</v>
@@ -47835,10 +48117,10 @@
         <v>27</v>
       </c>
       <c r="H442" s="1" t="s">
-        <v>271</v>
+        <v>1364</v>
       </c>
       <c r="I442" s="1" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="J442" s="1" t="s">
         <v>27</v>
@@ -47847,31 +48129,31 @@
         <v>27</v>
       </c>
       <c r="L442" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M442" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M442" s="1">
+        <v>1</v>
       </c>
       <c r="N442" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O442" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P442" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Q442" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R442" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S442" s="1" t="s">
-        <v>366</v>
+        <v>128</v>
       </c>
       <c r="T442" s="1" t="s">
-        <v>1581</v>
+        <v>1545</v>
       </c>
       <c r="U442" s="1" t="s">
         <v>27</v>
@@ -47880,29 +48162,31 @@
         <v>27</v>
       </c>
       <c r="W442" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="X442" s="1"/>
+        <v>1365</v>
+      </c>
+      <c r="X442" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y442" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z442" s="1" t="s">
-        <v>1585</v>
+        <v>1536</v>
       </c>
       <c r="AA442" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB442" s="1" t="s">
-        <v>27</v>
+        <v>1544</v>
       </c>
       <c r="AC442" s="1" t="s">
-        <v>27</v>
+        <v>1563</v>
       </c>
       <c r="AD442" s="1" t="s">
-        <v>27</v>
+        <v>1366</v>
       </c>
       <c r="AE442" s="1" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="443" spans="1:31" x14ac:dyDescent="0.45">
@@ -47919,7 +48203,7 @@
         <v>26</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="F443" s="1" t="s">
         <v>27</v>
@@ -47928,7 +48212,7 @@
         <v>27</v>
       </c>
       <c r="H443" s="1" t="s">
-        <v>1692</v>
+        <v>271</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>27</v>
@@ -47940,31 +48224,31 @@
         <v>27</v>
       </c>
       <c r="L443" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M443" s="1">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="M443" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N443" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O443" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P443" s="1" t="s">
-        <v>885</v>
+        <v>27</v>
       </c>
       <c r="Q443" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R443" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S443" s="1" t="s">
-        <v>1376</v>
+        <v>366</v>
       </c>
       <c r="T443" s="1" t="s">
-        <v>1545</v>
+        <v>1581</v>
       </c>
       <c r="U443" s="1" t="s">
         <v>27</v>
@@ -47973,29 +48257,31 @@
         <v>27</v>
       </c>
       <c r="W443" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="X443" s="1"/>
+        <v>1372</v>
+      </c>
+      <c r="X443" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y443" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z443" s="1" t="s">
-        <v>1536</v>
+        <v>1585</v>
       </c>
       <c r="AA443" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB443" s="1" t="s">
-        <v>1580</v>
+        <v>27</v>
       </c>
       <c r="AC443" s="1" t="s">
-        <v>1563</v>
+        <v>27</v>
       </c>
       <c r="AD443" s="1" t="s">
-        <v>1377</v>
+        <v>27</v>
       </c>
       <c r="AE443" s="1" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="444" spans="1:31" x14ac:dyDescent="0.45">
@@ -48021,7 +48307,7 @@
         <v>27</v>
       </c>
       <c r="H444" s="1" t="s">
-        <v>61</v>
+        <v>1692</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>27</v>
@@ -48045,7 +48331,7 @@
         <v>29</v>
       </c>
       <c r="P444" s="1" t="s">
-        <v>30</v>
+        <v>885</v>
       </c>
       <c r="Q444" s="1" t="s">
         <v>31</v>
@@ -48066,9 +48352,11 @@
         <v>27</v>
       </c>
       <c r="W444" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="X444" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="X444" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y444" s="1" t="s">
         <v>1541</v>
       </c>
@@ -48096,28 +48384,28 @@
         <v>1368</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>1378</v>
+        <v>1369</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>1379</v>
+        <v>1370</v>
       </c>
       <c r="D445" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>1342</v>
+        <v>1374</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>837</v>
+        <v>27</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="H445" s="1" t="s">
-        <v>1380</v>
+        <v>61</v>
       </c>
       <c r="I445" s="1" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="J445" s="1" t="s">
         <v>27</v>
@@ -48126,19 +48414,19 @@
         <v>27</v>
       </c>
       <c r="L445" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M445" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M445" s="1">
+        <v>1</v>
       </c>
       <c r="N445" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O445" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P445" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Q445" s="1" t="s">
         <v>31</v>
@@ -48147,10 +48435,10 @@
         <v>31</v>
       </c>
       <c r="S445" s="1" t="s">
-        <v>249</v>
+        <v>1376</v>
       </c>
       <c r="T445" s="1" t="s">
-        <v>1581</v>
+        <v>1545</v>
       </c>
       <c r="U445" s="1" t="s">
         <v>27</v>
@@ -48159,11 +48447,13 @@
         <v>27</v>
       </c>
       <c r="W445" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X445" s="1"/>
+        <v>1097</v>
+      </c>
+      <c r="X445" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y445" s="1" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="Z445" s="1" t="s">
         <v>1536</v>
@@ -48172,16 +48462,16 @@
         <v>27</v>
       </c>
       <c r="AB445" s="1" t="s">
-        <v>27</v>
+        <v>1580</v>
       </c>
       <c r="AC445" s="1" t="s">
-        <v>27</v>
+        <v>1563</v>
       </c>
       <c r="AD445" s="1" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="AE445" s="1" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="446" spans="1:31" x14ac:dyDescent="0.45">
@@ -48201,16 +48491,16 @@
         <v>1342</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>27</v>
+        <v>837</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="H446" s="1" t="s">
-        <v>39</v>
+        <v>1380</v>
       </c>
       <c r="I446" s="1" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="J446" s="1" t="s">
         <v>27</v>
@@ -48219,19 +48509,19 @@
         <v>27</v>
       </c>
       <c r="L446" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M446" s="1">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="M446" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N446" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O446" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P446" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q446" s="1" t="s">
         <v>31</v>
@@ -48240,10 +48530,10 @@
         <v>31</v>
       </c>
       <c r="S446" s="1" t="s">
-        <v>92</v>
+        <v>249</v>
       </c>
       <c r="T446" s="1" t="s">
-        <v>1545</v>
+        <v>1581</v>
       </c>
       <c r="U446" s="1" t="s">
         <v>27</v>
@@ -48252,11 +48542,13 @@
         <v>27</v>
       </c>
       <c r="W446" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="X446" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X446" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y446" s="1" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="Z446" s="1" t="s">
         <v>1536</v>
@@ -48271,7 +48563,7 @@
         <v>27</v>
       </c>
       <c r="AD446" s="1" t="s">
-        <v>27</v>
+        <v>1381</v>
       </c>
       <c r="AE446" s="1" t="s">
         <v>1382</v>
@@ -48282,16 +48574,16 @@
         <v>1368</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>1385</v>
+        <v>1342</v>
       </c>
       <c r="F447" s="1" t="s">
         <v>27</v>
@@ -48300,7 +48592,7 @@
         <v>27</v>
       </c>
       <c r="H447" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>27</v>
@@ -48312,31 +48604,31 @@
         <v>27</v>
       </c>
       <c r="L447" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M447" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M447" s="1">
+        <v>1</v>
       </c>
       <c r="N447" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O447" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P447" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Q447" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R447" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S447" s="1" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="T447" s="1" t="s">
-        <v>27</v>
+        <v>1545</v>
       </c>
       <c r="U447" s="1" t="s">
         <v>27</v>
@@ -48345,11 +48637,13 @@
         <v>27</v>
       </c>
       <c r="W447" s="1" t="s">
-        <v>1477</v>
-      </c>
-      <c r="X447" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="X447" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y447" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z447" s="1" t="s">
         <v>1536</v>
@@ -48358,33 +48652,33 @@
         <v>27</v>
       </c>
       <c r="AB447" s="1" t="s">
-        <v>1580</v>
+        <v>27</v>
       </c>
       <c r="AC447" s="1" t="s">
-        <v>1563</v>
+        <v>27</v>
       </c>
       <c r="AD447" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AE447" s="1" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="448" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
-        <v>1387</v>
+        <v>1368</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>622</v>
+        <v>1385</v>
       </c>
       <c r="F448" s="1" t="s">
         <v>27</v>
@@ -48393,7 +48687,7 @@
         <v>27</v>
       </c>
       <c r="H448" s="1" t="s">
-        <v>1390</v>
+        <v>55</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>27</v>
@@ -48405,31 +48699,31 @@
         <v>27</v>
       </c>
       <c r="L448" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M448" s="1">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="M448" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N448" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O448" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P448" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q448" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R448" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S448" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="T448" s="1" t="s">
-        <v>1545</v>
+        <v>27</v>
       </c>
       <c r="U448" s="1" t="s">
         <v>27</v>
@@ -48438,29 +48732,31 @@
         <v>27</v>
       </c>
       <c r="W448" s="1" t="s">
-        <v>1391</v>
-      </c>
-      <c r="X448" s="1"/>
+        <v>1477</v>
+      </c>
+      <c r="X448" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y448" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z448" s="1" t="s">
-        <v>27</v>
+        <v>1536</v>
       </c>
       <c r="AA448" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB448" s="1" t="s">
-        <v>27</v>
+        <v>1580</v>
       </c>
       <c r="AC448" s="1" t="s">
-        <v>27</v>
+        <v>1563</v>
       </c>
       <c r="AD448" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AE448" s="1" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="449" spans="1:31" x14ac:dyDescent="0.45">
@@ -48476,8 +48772,8 @@
       <c r="D449" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E449" s="1">
-        <v>1931</v>
+      <c r="E449" s="1" t="s">
+        <v>622</v>
       </c>
       <c r="F449" s="1" t="s">
         <v>27</v>
@@ -48486,7 +48782,7 @@
         <v>27</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>61</v>
+        <v>1390</v>
       </c>
       <c r="I449" s="1" t="s">
         <v>27</v>
@@ -48500,23 +48796,23 @@
       <c r="L449" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M449" s="1" t="s">
-        <v>27</v>
+      <c r="M449" s="1">
+        <v>1</v>
       </c>
       <c r="N449" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O449" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P449" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Q449" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R449" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S449" s="1" t="s">
         <v>92</v>
@@ -48531,29 +48827,31 @@
         <v>27</v>
       </c>
       <c r="W449" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X449" s="1"/>
+        <v>1391</v>
+      </c>
+      <c r="X449" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y449" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z449" s="1" t="s">
-        <v>1536</v>
+        <v>27</v>
       </c>
       <c r="AA449" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB449" s="1" t="s">
-        <v>1537</v>
+        <v>27</v>
       </c>
       <c r="AC449" s="1" t="s">
-        <v>1543</v>
+        <v>27</v>
       </c>
       <c r="AD449" s="1" t="s">
-        <v>1393</v>
+        <v>27</v>
       </c>
       <c r="AE449" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="450" spans="1:31" x14ac:dyDescent="0.45">
@@ -48561,16 +48859,16 @@
         <v>1387</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>1530</v>
+        <v>1388</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E450" s="1" t="s">
-        <v>1396</v>
+        <v>37</v>
+      </c>
+      <c r="E450" s="1">
+        <v>1931</v>
       </c>
       <c r="F450" s="1" t="s">
         <v>27</v>
@@ -48579,10 +48877,10 @@
         <v>27</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>1397</v>
+        <v>61</v>
       </c>
       <c r="I450" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J450" s="1" t="s">
         <v>27</v>
@@ -48591,28 +48889,28 @@
         <v>27</v>
       </c>
       <c r="L450" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M450" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N450" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O450" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P450" s="1" t="s">
-        <v>449</v>
+        <v>27</v>
       </c>
       <c r="Q450" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R450" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S450" s="1" t="s">
-        <v>318</v>
+        <v>92</v>
       </c>
       <c r="T450" s="1" t="s">
         <v>1545</v>
@@ -48624,11 +48922,13 @@
         <v>27</v>
       </c>
       <c r="W450" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X450" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X450" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y450" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z450" s="1" t="s">
         <v>1536</v>
@@ -48643,10 +48943,10 @@
         <v>1543</v>
       </c>
       <c r="AD450" s="1" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="AE450" s="1" t="s">
-        <v>1693</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="451" spans="1:31" x14ac:dyDescent="0.45">
@@ -48717,11 +49017,13 @@
         <v>27</v>
       </c>
       <c r="W451" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="X451" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X451" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y451" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z451" s="1" t="s">
         <v>1536</v>
@@ -48810,11 +49112,13 @@
         <v>27</v>
       </c>
       <c r="W452" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="X452" s="1"/>
+        <v>226</v>
+      </c>
+      <c r="X452" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y452" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z452" s="1" t="s">
         <v>1536</v>
@@ -48903,14 +49207,16 @@
         <v>27</v>
       </c>
       <c r="W453" s="1" t="s">
-        <v>1523</v>
-      </c>
-      <c r="X453" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="X453" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y453" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z453" s="1" t="s">
-        <v>27</v>
+        <v>1536</v>
       </c>
       <c r="AA453" s="1" t="s">
         <v>27</v>
@@ -48951,10 +49257,10 @@
         <v>27</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="I454" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J454" s="1" t="s">
         <v>27</v>
@@ -48963,19 +49269,19 @@
         <v>27</v>
       </c>
       <c r="L454" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M454" s="1">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="M454" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N454" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="O454" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="P454" s="1" t="s">
-        <v>1400</v>
+        <v>449</v>
       </c>
       <c r="Q454" s="1" t="s">
         <v>31</v>
@@ -48984,7 +49290,7 @@
         <v>31</v>
       </c>
       <c r="S454" s="1" t="s">
-        <v>128</v>
+        <v>318</v>
       </c>
       <c r="T454" s="1" t="s">
         <v>1545</v>
@@ -48996,29 +49302,31 @@
         <v>27</v>
       </c>
       <c r="W454" s="1" t="s">
-        <v>1477</v>
-      </c>
-      <c r="X454" s="1"/>
+        <v>1736</v>
+      </c>
+      <c r="X454" s="1" t="s">
+        <v>1523</v>
+      </c>
       <c r="Y454" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z454" s="1" t="s">
-        <v>1536</v>
+        <v>27</v>
       </c>
       <c r="AA454" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB454" s="1" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="AC454" s="1" t="s">
         <v>1543</v>
       </c>
       <c r="AD454" s="1" t="s">
-        <v>69</v>
+        <v>1398</v>
       </c>
       <c r="AE454" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="455" spans="1:31" x14ac:dyDescent="0.45">
@@ -49089,11 +49397,13 @@
         <v>27</v>
       </c>
       <c r="W455" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="X455" s="1"/>
+        <v>1477</v>
+      </c>
+      <c r="X455" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y455" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z455" s="1" t="s">
         <v>1536</v>
@@ -49182,14 +49492,16 @@
         <v>27</v>
       </c>
       <c r="W456" s="1" t="s">
-        <v>1524</v>
-      </c>
-      <c r="X456" s="1"/>
+        <v>1365</v>
+      </c>
+      <c r="X456" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y456" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z456" s="1" t="s">
-        <v>27</v>
+        <v>1536</v>
       </c>
       <c r="AA456" s="1" t="s">
         <v>27</v>
@@ -49220,8 +49532,8 @@
       <c r="D457" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E457" s="1">
-        <v>1943</v>
+      <c r="E457" s="1" t="s">
+        <v>1396</v>
       </c>
       <c r="F457" s="1" t="s">
         <v>27</v>
@@ -49230,10 +49542,10 @@
         <v>27</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>61</v>
+        <v>1399</v>
       </c>
       <c r="I457" s="1" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="J457" s="1" t="s">
         <v>27</v>
@@ -49245,16 +49557,16 @@
         <v>28</v>
       </c>
       <c r="M457" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N457" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="O457" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="P457" s="1" t="s">
-        <v>30</v>
+        <v>1400</v>
       </c>
       <c r="Q457" s="1" t="s">
         <v>31</v>
@@ -49275,20 +49587,22 @@
         <v>27</v>
       </c>
       <c r="W457" s="1" t="s">
-        <v>1401</v>
-      </c>
-      <c r="X457" s="1"/>
+        <v>1391</v>
+      </c>
+      <c r="X457" s="1" t="s">
+        <v>1524</v>
+      </c>
       <c r="Y457" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z457" s="1" t="s">
-        <v>1536</v>
+        <v>27</v>
       </c>
       <c r="AA457" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB457" s="1" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="AC457" s="1" t="s">
         <v>1543</v>
@@ -49297,7 +49611,7 @@
         <v>69</v>
       </c>
       <c r="AE457" s="1" t="s">
-        <v>1402</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="458" spans="1:31" x14ac:dyDescent="0.45">
@@ -49305,16 +49619,16 @@
         <v>1387</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="D458" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E458" s="1" t="s">
-        <v>1404</v>
+      <c r="E458" s="1">
+        <v>1943</v>
       </c>
       <c r="F458" s="1" t="s">
         <v>27</v>
@@ -49323,7 +49637,7 @@
         <v>27</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>27</v>
@@ -49337,29 +49651,29 @@
       <c r="L458" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M458" s="1" t="s">
-        <v>27</v>
+      <c r="M458" s="1">
+        <v>1</v>
       </c>
       <c r="N458" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="O458" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="P458" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Q458" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R458" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S458" s="1" t="s">
-        <v>1361</v>
+        <v>128</v>
       </c>
       <c r="T458" s="1" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="U458" s="1" t="s">
         <v>27</v>
@@ -49368,9 +49682,11 @@
         <v>27</v>
       </c>
       <c r="W458" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X458" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X458" s="1" t="s">
+        <v>1401</v>
+      </c>
       <c r="Y458" s="1" t="s">
         <v>27</v>
       </c>
@@ -49381,16 +49697,16 @@
         <v>27</v>
       </c>
       <c r="AB458" s="1" t="s">
-        <v>27</v>
+        <v>1537</v>
       </c>
       <c r="AC458" s="1" t="s">
-        <v>27</v>
+        <v>1543</v>
       </c>
       <c r="AD458" s="1" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="AE458" s="1" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="459" spans="1:31" x14ac:dyDescent="0.45">
@@ -49461,9 +49777,11 @@
         <v>27</v>
       </c>
       <c r="W459" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X459" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X459" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y459" s="1" t="s">
         <v>27</v>
       </c>
@@ -49554,14 +49872,16 @@
         <v>27</v>
       </c>
       <c r="W460" s="1" t="s">
-        <v>1525</v>
-      </c>
-      <c r="X460" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X460" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y460" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z460" s="1" t="s">
-        <v>1579</v>
+        <v>1536</v>
       </c>
       <c r="AA460" s="1" t="s">
         <v>27</v>
@@ -49593,7 +49913,7 @@
         <v>172</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="F461" s="1" t="s">
         <v>27</v>
@@ -49602,10 +49922,10 @@
         <v>27</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>630</v>
+        <v>135</v>
       </c>
       <c r="I461" s="1" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="J461" s="1" t="s">
         <v>27</v>
@@ -49620,10 +49940,10 @@
         <v>27</v>
       </c>
       <c r="N461" s="1" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="O461" s="1" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="P461" s="1" t="s">
         <v>27</v>
@@ -49635,10 +49955,10 @@
         <v>27</v>
       </c>
       <c r="S461" s="1" t="s">
-        <v>27</v>
+        <v>1361</v>
       </c>
       <c r="T461" s="1" t="s">
-        <v>27</v>
+        <v>1540</v>
       </c>
       <c r="U461" s="1" t="s">
         <v>27</v>
@@ -49647,29 +49967,31 @@
         <v>27</v>
       </c>
       <c r="W461" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X461" s="1"/>
+        <v>1755</v>
+      </c>
+      <c r="X461" s="1" t="s">
+        <v>1525</v>
+      </c>
       <c r="Y461" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z461" s="1" t="s">
-        <v>1536</v>
+        <v>1579</v>
       </c>
       <c r="AA461" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB461" s="1" t="s">
-        <v>1537</v>
+        <v>27</v>
       </c>
       <c r="AC461" s="1" t="s">
-        <v>1543</v>
+        <v>27</v>
       </c>
       <c r="AD461" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AE461" s="1" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="462" spans="1:31" x14ac:dyDescent="0.45">
@@ -49677,16 +49999,16 @@
         <v>1387</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>1408</v>
+        <v>1531</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>1409</v>
+        <v>1403</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>438</v>
+        <v>172</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>27</v>
+        <v>1406</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>27</v>
@@ -49695,10 +50017,10 @@
         <v>27</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>39</v>
+        <v>630</v>
       </c>
       <c r="I462" s="1" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="J462" s="1" t="s">
         <v>27</v>
@@ -49709,29 +50031,29 @@
       <c r="L462" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M462" s="1">
-        <v>1</v>
+      <c r="M462" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N462" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O462" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P462" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q462" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R462" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S462" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="T462" s="1" t="s">
-        <v>1545</v>
+        <v>27</v>
       </c>
       <c r="U462" s="1" t="s">
         <v>27</v>
@@ -49740,9 +50062,11 @@
         <v>27</v>
       </c>
       <c r="W462" s="1" t="s">
-        <v>1526</v>
-      </c>
-      <c r="X462" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X462" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y462" s="1" t="s">
         <v>1541</v>
       </c>
@@ -49753,7 +50077,7 @@
         <v>27</v>
       </c>
       <c r="AB462" s="1" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="AC462" s="1" t="s">
         <v>1543</v>
@@ -49762,7 +50086,7 @@
         <v>27</v>
       </c>
       <c r="AE462" s="1" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="463" spans="1:31" x14ac:dyDescent="0.45">
@@ -49833,9 +50157,11 @@
         <v>27</v>
       </c>
       <c r="W463" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="X463" s="1"/>
+        <v>1748</v>
+      </c>
+      <c r="X463" s="1" t="s">
+        <v>1526</v>
+      </c>
       <c r="Y463" s="1" t="s">
         <v>1541</v>
       </c>
@@ -49926,9 +50252,11 @@
         <v>27</v>
       </c>
       <c r="W464" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X464" s="1"/>
+        <v>1365</v>
+      </c>
+      <c r="X464" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y464" s="1" t="s">
         <v>1541</v>
       </c>
@@ -50019,11 +50347,13 @@
         <v>27</v>
       </c>
       <c r="W465" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X465" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X465" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y465" s="1" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="Z465" s="1" t="s">
         <v>1536</v>
@@ -50049,31 +50379,31 @@
         <v>1387</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="D466" s="1" t="s">
         <v>438</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>1413</v>
+        <v>27</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>1414</v>
+        <v>27</v>
       </c>
       <c r="G466" s="1" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="H466" s="1" t="s">
-        <v>1415</v>
+        <v>39</v>
       </c>
       <c r="I466" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J466" s="1" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="K466" s="1" t="s">
         <v>27</v>
@@ -50081,17 +50411,17 @@
       <c r="L466" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M466" s="1" t="s">
-        <v>108</v>
+      <c r="M466" s="1">
+        <v>1</v>
       </c>
       <c r="N466" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="O466" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="P466" s="1" t="s">
-        <v>1226</v>
+        <v>40</v>
       </c>
       <c r="Q466" s="1" t="s">
         <v>31</v>
@@ -50112,11 +50442,13 @@
         <v>27</v>
       </c>
       <c r="W466" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X466" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X466" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y466" s="1" t="s">
-        <v>27</v>
+        <v>1547</v>
       </c>
       <c r="Z466" s="1" t="s">
         <v>1536</v>
@@ -50125,16 +50457,16 @@
         <v>27</v>
       </c>
       <c r="AB466" s="1" t="s">
-        <v>27</v>
+        <v>1544</v>
       </c>
       <c r="AC466" s="1" t="s">
-        <v>27</v>
+        <v>1543</v>
       </c>
       <c r="AD466" s="1" t="s">
-        <v>1416</v>
+        <v>27</v>
       </c>
       <c r="AE466" s="1" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="467" spans="1:31" x14ac:dyDescent="0.45">
@@ -50205,11 +50537,13 @@
         <v>27</v>
       </c>
       <c r="W467" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="X467" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X467" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y467" s="1" t="s">
-        <v>1541</v>
+        <v>27</v>
       </c>
       <c r="Z467" s="1" t="s">
         <v>1536</v>
@@ -50298,14 +50632,16 @@
         <v>27</v>
       </c>
       <c r="W468" s="1" t="s">
-        <v>1527</v>
-      </c>
-      <c r="X468" s="1"/>
+        <v>310</v>
+      </c>
+      <c r="X468" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y468" s="1" t="s">
-        <v>27</v>
+        <v>1541</v>
       </c>
       <c r="Z468" s="1" t="s">
-        <v>1579</v>
+        <v>1536</v>
       </c>
       <c r="AA468" s="1" t="s">
         <v>27</v>
@@ -50325,34 +50661,34 @@
     </row>
     <row r="469" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A469" s="1" t="s">
-        <v>1418</v>
+        <v>1387</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>172</v>
+        <v>438</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
       <c r="G469" s="1" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="H469" s="1" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>126</v>
       </c>
       <c r="J469" s="1" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="K469" s="1" t="s">
         <v>27</v>
@@ -50360,17 +50696,17 @@
       <c r="L469" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M469" s="1">
-        <v>1</v>
+      <c r="M469" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="N469" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="O469" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="P469" s="1" t="s">
-        <v>30</v>
+        <v>1226</v>
       </c>
       <c r="Q469" s="1" t="s">
         <v>31</v>
@@ -50379,7 +50715,7 @@
         <v>31</v>
       </c>
       <c r="S469" s="1" t="s">
-        <v>1321</v>
+        <v>92</v>
       </c>
       <c r="T469" s="1" t="s">
         <v>1545</v>
@@ -50391,29 +50727,31 @@
         <v>27</v>
       </c>
       <c r="W469" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="X469" s="1"/>
+        <v>1755</v>
+      </c>
+      <c r="X469" s="1" t="s">
+        <v>1527</v>
+      </c>
       <c r="Y469" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="Z469" s="1" t="s">
-        <v>1536</v>
+        <v>1579</v>
       </c>
       <c r="AA469" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AB469" s="1" t="s">
-        <v>1537</v>
+        <v>27</v>
       </c>
       <c r="AC469" s="1" t="s">
-        <v>1543</v>
+        <v>27</v>
       </c>
       <c r="AD469" s="1" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
       <c r="AE469" s="1" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="470" spans="1:31" x14ac:dyDescent="0.45">
@@ -50430,19 +50768,19 @@
         <v>172</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>27</v>
+        <v>1422</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="H470" s="1" t="s">
-        <v>1053</v>
+        <v>1423</v>
       </c>
       <c r="I470" s="1" t="s">
-        <v>1570</v>
+        <v>126</v>
       </c>
       <c r="J470" s="1" t="s">
         <v>27</v>
@@ -50451,31 +50789,31 @@
         <v>27</v>
       </c>
       <c r="L470" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M470" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M470" s="1">
+        <v>1</v>
       </c>
       <c r="N470" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O470" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P470" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Q470" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R470" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S470" s="1" t="s">
-        <v>27</v>
+        <v>1321</v>
       </c>
       <c r="T470" s="1" t="s">
-        <v>27</v>
+        <v>1545</v>
       </c>
       <c r="U470" s="1" t="s">
         <v>27</v>
@@ -50484,11 +50822,13 @@
         <v>27</v>
       </c>
       <c r="W470" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X470" s="1"/>
+        <v>551</v>
+      </c>
+      <c r="X470" s="1" t="s">
+        <v>810</v>
+      </c>
       <c r="Y470" s="1" t="s">
-        <v>1547</v>
+        <v>71</v>
       </c>
       <c r="Z470" s="1" t="s">
         <v>1536</v>
@@ -50497,16 +50837,16 @@
         <v>27</v>
       </c>
       <c r="AB470" s="1" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="AC470" s="1" t="s">
         <v>1543</v>
       </c>
       <c r="AD470" s="1" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="AE470" s="1" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="471" spans="1:31" x14ac:dyDescent="0.45">
@@ -50577,11 +50917,13 @@
         <v>27</v>
       </c>
       <c r="W471" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X471" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X471" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y471" s="1" t="s">
-        <v>27</v>
+        <v>1547</v>
       </c>
       <c r="Z471" s="1" t="s">
         <v>1536</v>
@@ -50670,9 +51012,11 @@
         <v>27</v>
       </c>
       <c r="W472" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="X472" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X472" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y472" s="1" t="s">
         <v>27</v>
       </c>
@@ -50700,16 +51044,16 @@
         <v>1418</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>27</v>
+        <v>1426</v>
       </c>
       <c r="F473" s="1" t="s">
         <v>27</v>
@@ -50718,46 +51062,46 @@
         <v>27</v>
       </c>
       <c r="H473" s="1" t="s">
-        <v>1431</v>
+        <v>1053</v>
       </c>
       <c r="I473" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J473" s="1">
-        <v>1</v>
+        <v>1570</v>
+      </c>
+      <c r="J473" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="K473" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L473" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M473" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N473" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="O473" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="P473" s="1" t="s">
-        <v>1432</v>
+        <v>27</v>
       </c>
       <c r="Q473" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R473" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S473" s="1" t="s">
-        <v>1695</v>
+        <v>27</v>
       </c>
       <c r="T473" s="1" t="s">
-        <v>1545</v>
+        <v>27</v>
       </c>
       <c r="U473" s="1" t="s">
-        <v>1433</v>
+        <v>27</v>
       </c>
       <c r="V473" s="1" t="s">
         <v>27</v>
@@ -50765,7 +51109,9 @@
       <c r="W473" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="X473" s="1"/>
+      <c r="X473" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y473" s="1" t="s">
         <v>27</v>
       </c>
@@ -50782,10 +51128,10 @@
         <v>1543</v>
       </c>
       <c r="AD473" s="1" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
       <c r="AE473" s="1" t="s">
-        <v>1435</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="474" spans="1:31" x14ac:dyDescent="0.45">
@@ -50801,8 +51147,8 @@
       <c r="D474" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E474" s="1">
-        <v>1947</v>
+      <c r="E474" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F474" s="1" t="s">
         <v>27</v>
@@ -50811,13 +51157,13 @@
         <v>27</v>
       </c>
       <c r="H474" s="1" t="s">
-        <v>61</v>
+        <v>1431</v>
       </c>
       <c r="I474" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J474" s="1" t="s">
-        <v>27</v>
+        <v>126</v>
+      </c>
+      <c r="J474" s="1">
+        <v>1</v>
       </c>
       <c r="K474" s="1" t="s">
         <v>27</v>
@@ -50826,39 +51172,41 @@
         <v>28</v>
       </c>
       <c r="M474" s="1" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="N474" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="O474" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="P474" s="1" t="s">
-        <v>1732</v>
+        <v>1432</v>
       </c>
       <c r="Q474" s="1" t="s">
-        <v>1436</v>
+        <v>31</v>
       </c>
       <c r="R474" s="1" t="s">
-        <v>1730</v>
+        <v>31</v>
       </c>
       <c r="S474" s="1" t="s">
-        <v>1437</v>
+        <v>1695</v>
       </c>
       <c r="T474" s="1" t="s">
         <v>1545</v>
       </c>
       <c r="U474" s="1" t="s">
-        <v>27</v>
+        <v>1433</v>
       </c>
       <c r="V474" s="1" t="s">
         <v>27</v>
       </c>
       <c r="W474" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X474" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="X474" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y474" s="1" t="s">
         <v>27</v>
       </c>
@@ -50869,16 +51217,16 @@
         <v>27</v>
       </c>
       <c r="AB474" s="1" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="AC474" s="1" t="s">
         <v>1543</v>
       </c>
       <c r="AD474" s="1" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="AE474" s="1" t="s">
-        <v>1696</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="475" spans="1:31" x14ac:dyDescent="0.45">
@@ -50894,8 +51242,8 @@
       <c r="D475" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E475" s="1" t="s">
-        <v>27</v>
+      <c r="E475" s="1">
+        <v>1947</v>
       </c>
       <c r="F475" s="1" t="s">
         <v>27</v>
@@ -50904,10 +51252,10 @@
         <v>27</v>
       </c>
       <c r="H475" s="1" t="s">
-        <v>1440</v>
+        <v>61</v>
       </c>
       <c r="I475" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J475" s="1" t="s">
         <v>27</v>
@@ -50916,31 +51264,31 @@
         <v>27</v>
       </c>
       <c r="L475" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M475" s="1" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="N475" s="1" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="O475" s="1" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="P475" s="1" t="s">
-        <v>27</v>
+        <v>1732</v>
       </c>
       <c r="Q475" s="1" t="s">
-        <v>27</v>
+        <v>1436</v>
       </c>
       <c r="R475" s="1" t="s">
-        <v>27</v>
+        <v>1730</v>
       </c>
       <c r="S475" s="1" t="s">
-        <v>27</v>
+        <v>1437</v>
       </c>
       <c r="T475" s="1" t="s">
-        <v>27</v>
+        <v>1545</v>
       </c>
       <c r="U475" s="1" t="s">
         <v>27</v>
@@ -50949,9 +51297,11 @@
         <v>27</v>
       </c>
       <c r="W475" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="X475" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X475" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y475" s="1" t="s">
         <v>27</v>
       </c>
@@ -50962,16 +51312,16 @@
         <v>27</v>
       </c>
       <c r="AB475" s="1" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="AC475" s="1" t="s">
         <v>1543</v>
       </c>
       <c r="AD475" s="1" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="AE475" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="476" spans="1:31" x14ac:dyDescent="0.45">
@@ -50997,10 +51347,10 @@
         <v>27</v>
       </c>
       <c r="H476" s="1" t="s">
-        <v>39</v>
+        <v>1440</v>
       </c>
       <c r="I476" s="1" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="J476" s="1" t="s">
         <v>27</v>
@@ -51009,31 +51359,31 @@
         <v>27</v>
       </c>
       <c r="L476" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M476" s="1">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="M476" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N476" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O476" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P476" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q476" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R476" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S476" s="1" t="s">
-        <v>207</v>
+        <v>27</v>
       </c>
       <c r="T476" s="1" t="s">
-        <v>1545</v>
+        <v>27</v>
       </c>
       <c r="U476" s="1" t="s">
         <v>27</v>
@@ -51042,9 +51392,11 @@
         <v>27</v>
       </c>
       <c r="W476" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X476" s="1"/>
+        <v>1365</v>
+      </c>
+      <c r="X476" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y476" s="1" t="s">
         <v>27</v>
       </c>
@@ -51061,10 +51413,10 @@
         <v>1543</v>
       </c>
       <c r="AD476" s="1" t="s">
-        <v>27</v>
+        <v>1441</v>
       </c>
       <c r="AE476" s="1" t="s">
-        <v>1442</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="477" spans="1:31" x14ac:dyDescent="0.45">
@@ -51072,13 +51424,13 @@
         <v>1418</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>1444</v>
+        <v>1430</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>27</v>
@@ -51090,10 +51442,10 @@
         <v>27</v>
       </c>
       <c r="H477" s="1" t="s">
-        <v>1699</v>
+        <v>39</v>
       </c>
       <c r="I477" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J477" s="1" t="s">
         <v>27</v>
@@ -51108,22 +51460,22 @@
         <v>1</v>
       </c>
       <c r="N477" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="O477" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="P477" s="1" t="s">
-        <v>1700</v>
+        <v>40</v>
       </c>
       <c r="Q477" s="1" t="s">
-        <v>1436</v>
+        <v>31</v>
       </c>
       <c r="R477" s="1" t="s">
-        <v>1730</v>
+        <v>31</v>
       </c>
       <c r="S477" s="1" t="s">
-        <v>128</v>
+        <v>207</v>
       </c>
       <c r="T477" s="1" t="s">
         <v>1545</v>
@@ -51132,12 +51484,14 @@
         <v>27</v>
       </c>
       <c r="V477" s="1" t="s">
-        <v>1447</v>
+        <v>27</v>
       </c>
       <c r="W477" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="X477" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X477" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y477" s="1" t="s">
         <v>27</v>
       </c>
@@ -51148,16 +51502,16 @@
         <v>27</v>
       </c>
       <c r="AB477" s="1" t="s">
-        <v>1580</v>
+        <v>1544</v>
       </c>
       <c r="AC477" s="1" t="s">
-        <v>1563</v>
+        <v>1543</v>
       </c>
       <c r="AD477" s="1" t="s">
-        <v>1448</v>
+        <v>27</v>
       </c>
       <c r="AE477" s="1" t="s">
-        <v>1698</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="478" spans="1:31" x14ac:dyDescent="0.45">
@@ -51183,10 +51537,10 @@
         <v>27</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>1445</v>
+        <v>1699</v>
       </c>
       <c r="I478" s="1" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="J478" s="1" t="s">
         <v>27</v>
@@ -51201,16 +51555,16 @@
         <v>1</v>
       </c>
       <c r="N478" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="O478" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="P478" s="1" t="s">
-        <v>1446</v>
+        <v>1700</v>
       </c>
       <c r="Q478" s="1" t="s">
-        <v>201</v>
+        <v>1436</v>
       </c>
       <c r="R478" s="1" t="s">
         <v>1730</v>
@@ -51228,9 +51582,11 @@
         <v>1447</v>
       </c>
       <c r="W478" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="X478" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="X478" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y478" s="1" t="s">
         <v>27</v>
       </c>
@@ -51241,7 +51597,7 @@
         <v>27</v>
       </c>
       <c r="AB478" s="1" t="s">
-        <v>1537</v>
+        <v>1580</v>
       </c>
       <c r="AC478" s="1" t="s">
         <v>1563</v>
@@ -51250,24 +51606,24 @@
         <v>1448</v>
       </c>
       <c r="AE478" s="1" t="s">
-        <v>1449</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="479" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A479" s="1" t="s">
-        <v>1450</v>
+        <v>1418</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>1453</v>
+        <v>27</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>27</v>
@@ -51276,7 +51632,7 @@
         <v>27</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>61</v>
+        <v>1445</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>27</v>
@@ -51288,42 +51644,44 @@
         <v>27</v>
       </c>
       <c r="L479" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M479" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M479" s="1">
+        <v>1</v>
       </c>
       <c r="N479" s="1" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="O479" s="1" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="P479" s="1" t="s">
-        <v>27</v>
+        <v>1446</v>
       </c>
       <c r="Q479" s="1" t="s">
-        <v>27</v>
+        <v>201</v>
       </c>
       <c r="R479" s="1" t="s">
-        <v>27</v>
+        <v>1730</v>
       </c>
       <c r="S479" s="1" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="T479" s="1" t="s">
-        <v>27</v>
+        <v>1545</v>
       </c>
       <c r="U479" s="1" t="s">
         <v>27</v>
       </c>
       <c r="V479" s="1" t="s">
-        <v>27</v>
+        <v>1447</v>
       </c>
       <c r="W479" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X479" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="X479" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y479" s="1" t="s">
         <v>27</v>
       </c>
@@ -51337,13 +51695,13 @@
         <v>1537</v>
       </c>
       <c r="AC479" s="1" t="s">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="AD479" s="1" t="s">
-        <v>27</v>
+        <v>1448</v>
       </c>
       <c r="AE479" s="1" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="480" spans="1:31" x14ac:dyDescent="0.45">
@@ -51351,31 +51709,31 @@
         <v>1450</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="D480" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>1458</v>
+        <v>27</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>1111</v>
+        <v>61</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J480" s="1" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="K480" s="1" t="s">
         <v>27</v>
@@ -51416,7 +51774,9 @@
       <c r="W480" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="X480" s="1"/>
+      <c r="X480" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y480" s="1" t="s">
         <v>27</v>
       </c>
@@ -51436,7 +51796,7 @@
         <v>27</v>
       </c>
       <c r="AE480" s="1" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="481" spans="1:31" x14ac:dyDescent="0.45">
@@ -51507,9 +51867,11 @@
         <v>27</v>
       </c>
       <c r="W481" s="1" t="s">
-        <v>1528</v>
-      </c>
-      <c r="X481" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X481" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y481" s="1" t="s">
         <v>27</v>
       </c>
@@ -51537,31 +51899,31 @@
         <v>1450</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="D482" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>27</v>
+        <v>1457</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>27</v>
+        <v>1458</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>55</v>
+        <v>1111</v>
       </c>
       <c r="I482" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J482" s="1" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="K482" s="1" t="s">
         <v>27</v>
@@ -51573,19 +51935,19 @@
         <v>27</v>
       </c>
       <c r="N482" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="O482" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="P482" s="1" t="s">
-        <v>1462</v>
+        <v>27</v>
       </c>
       <c r="Q482" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R482" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S482" s="1" t="s">
         <v>27</v>
@@ -51600,9 +51962,11 @@
         <v>27</v>
       </c>
       <c r="W482" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="X482" s="1"/>
+        <v>1736</v>
+      </c>
+      <c r="X482" s="1" t="s">
+        <v>1528</v>
+      </c>
       <c r="Y482" s="1" t="s">
         <v>27</v>
       </c>
@@ -51613,16 +51977,16 @@
         <v>27</v>
       </c>
       <c r="AB482" s="1" t="s">
-        <v>27</v>
+        <v>1537</v>
       </c>
       <c r="AC482" s="1" t="s">
-        <v>27</v>
+        <v>1543</v>
       </c>
       <c r="AD482" s="1" t="s">
-        <v>1463</v>
+        <v>27</v>
       </c>
       <c r="AE482" s="1" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="483" spans="1:31" x14ac:dyDescent="0.45">
@@ -51693,9 +52057,11 @@
         <v>27</v>
       </c>
       <c r="W483" s="1" t="s">
-        <v>1529</v>
-      </c>
-      <c r="X483" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="X483" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y483" s="1" t="s">
         <v>27</v>
       </c>
@@ -51732,7 +52098,7 @@
         <v>37</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>1465</v>
+        <v>27</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>27</v>
@@ -51741,10 +52107,10 @@
         <v>27</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>1466</v>
+        <v>55</v>
       </c>
       <c r="I484" s="1" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J484" s="1" t="s">
         <v>27</v>
@@ -51759,19 +52125,19 @@
         <v>27</v>
       </c>
       <c r="N484" s="1" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="O484" s="1" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="P484" s="1" t="s">
-        <v>27</v>
+        <v>1462</v>
       </c>
       <c r="Q484" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R484" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S484" s="1" t="s">
         <v>27</v>
@@ -51786,9 +52152,11 @@
         <v>27</v>
       </c>
       <c r="W484" s="1" t="s">
-        <v>1467</v>
-      </c>
-      <c r="X484" s="1"/>
+        <v>1736</v>
+      </c>
+      <c r="X484" s="1" t="s">
+        <v>1529</v>
+      </c>
       <c r="Y484" s="1" t="s">
         <v>27</v>
       </c>
@@ -51799,16 +52167,16 @@
         <v>27</v>
       </c>
       <c r="AB484" s="1" t="s">
-        <v>1544</v>
+        <v>27</v>
       </c>
       <c r="AC484" s="1" t="s">
-        <v>1543</v>
+        <v>27</v>
       </c>
       <c r="AD484" s="1" t="s">
-        <v>27</v>
+        <v>1463</v>
       </c>
       <c r="AE484" s="1" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="485" spans="1:31" x14ac:dyDescent="0.45">
@@ -51816,16 +52184,16 @@
         <v>1450</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1469</v>
+        <v>1460</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>1470</v>
+        <v>1461</v>
       </c>
       <c r="D485" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>27</v>
@@ -51834,10 +52202,10 @@
         <v>27</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>39</v>
+        <v>1466</v>
       </c>
       <c r="I485" s="1" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="J485" s="1" t="s">
         <v>27</v>
@@ -51846,31 +52214,31 @@
         <v>27</v>
       </c>
       <c r="L485" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M485" s="1">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="M485" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N485" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O485" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P485" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q485" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R485" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S485" s="1" t="s">
-        <v>1472</v>
+        <v>27</v>
       </c>
       <c r="T485" s="1" t="s">
-        <v>1540</v>
+        <v>27</v>
       </c>
       <c r="U485" s="1" t="s">
         <v>27</v>
@@ -51879,9 +52247,11 @@
         <v>27</v>
       </c>
       <c r="W485" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X485" s="1"/>
+        <v>1736</v>
+      </c>
+      <c r="X485" s="1" t="s">
+        <v>1467</v>
+      </c>
       <c r="Y485" s="1" t="s">
         <v>27</v>
       </c>
@@ -51898,10 +52268,10 @@
         <v>1543</v>
       </c>
       <c r="AD485" s="1" t="s">
-        <v>1473</v>
+        <v>27</v>
       </c>
       <c r="AE485" s="1" t="s">
-        <v>1701</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="486" spans="1:31" x14ac:dyDescent="0.45">
@@ -51927,7 +52297,7 @@
         <v>27</v>
       </c>
       <c r="H486" s="1" t="s">
-        <v>271</v>
+        <v>39</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>27</v>
@@ -51939,31 +52309,31 @@
         <v>27</v>
       </c>
       <c r="L486" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M486" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M486" s="1">
+        <v>1</v>
       </c>
       <c r="N486" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O486" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P486" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Q486" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R486" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S486" s="1" t="s">
-        <v>27</v>
+        <v>1472</v>
       </c>
       <c r="T486" s="1" t="s">
-        <v>27</v>
+        <v>1540</v>
       </c>
       <c r="U486" s="1" t="s">
         <v>27</v>
@@ -51972,9 +52342,11 @@
         <v>27</v>
       </c>
       <c r="W486" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="X486" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="X486" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y486" s="1" t="s">
         <v>27</v>
       </c>
@@ -51985,7 +52357,7 @@
         <v>27</v>
       </c>
       <c r="AB486" s="1" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="AC486" s="1" t="s">
         <v>1543</v>
@@ -51994,7 +52366,7 @@
         <v>1473</v>
       </c>
       <c r="AE486" s="1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="487" spans="1:31" x14ac:dyDescent="0.45">
@@ -52020,7 +52392,7 @@
         <v>27</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>39</v>
+        <v>271</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>27</v>
@@ -52053,10 +52425,10 @@
         <v>27</v>
       </c>
       <c r="S487" s="1" t="s">
-        <v>1474</v>
+        <v>27</v>
       </c>
       <c r="T487" s="1" t="s">
-        <v>1540</v>
+        <v>27</v>
       </c>
       <c r="U487" s="1" t="s">
         <v>27</v>
@@ -52065,9 +52437,11 @@
         <v>27</v>
       </c>
       <c r="W487" s="1" t="s">
-        <v>1477</v>
-      </c>
-      <c r="X487" s="1"/>
+        <v>1438</v>
+      </c>
+      <c r="X487" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y487" s="1" t="s">
         <v>27</v>
       </c>
@@ -52078,16 +52452,16 @@
         <v>27</v>
       </c>
       <c r="AB487" s="1" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="AC487" s="1" t="s">
         <v>1543</v>
       </c>
       <c r="AD487" s="1" t="s">
-        <v>27</v>
+        <v>1473</v>
       </c>
       <c r="AE487" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="488" spans="1:31" x14ac:dyDescent="0.45">
@@ -52158,14 +52532,16 @@
         <v>27</v>
       </c>
       <c r="W488" s="1" t="s">
-        <v>1391</v>
-      </c>
-      <c r="X488" s="1"/>
+        <v>1477</v>
+      </c>
+      <c r="X488" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="Y488" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Z488" s="1" t="s">
-        <v>27</v>
+        <v>1536</v>
       </c>
       <c r="AA488" s="1" t="s">
         <v>27</v>
@@ -52183,8 +52559,103 @@
         <v>1703</v>
       </c>
     </row>
+    <row r="489" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A489" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D489" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E489" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H489" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S489" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="T489" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="U489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W489" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="X489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB489" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="AC489" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AD489" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE489" s="1" t="s">
+        <v>1703</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="W1:W488" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="W1:W489" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data/craft learning1.xlsx
+++ b/Data/craft learning1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FilesVC\HRAF-2022\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C183870-FC03-4A21-BD37-E7BF25174411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5910B4-3E5F-41A7-82CA-BC3C43B43EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="craft learning" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'craft learning'!$Y$1:$Y$490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'craft learning'!$A$1:$AE$490</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14857" uniqueCount="1760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14858" uniqueCount="1760">
   <si>
     <t>Area</t>
   </si>
@@ -5278,9 +5278,6 @@
     <t>ritual item making</t>
   </si>
   <si>
-    <t>Miscellaneous</t>
-  </si>
-  <si>
     <t>leather working</t>
   </si>
   <si>
@@ -5306,6 +5303,9 @@
   </si>
   <si>
     <t>leather</t>
+  </si>
+  <si>
+    <t>miscellaneous</t>
   </si>
 </sst>
 </file>
@@ -5801,7 +5801,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5825,6 +5825,13 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -9699,10 +9706,10 @@
         <v>27</v>
       </c>
       <c r="W37" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X37" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X37" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y37" s="1" t="s">
         <v>27</v>
@@ -10275,7 +10282,7 @@
         <v>1475</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z43" s="1" t="s">
         <v>1533</v>
@@ -11985,7 +11992,7 @@
         <v>318</v>
       </c>
       <c r="Y61" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z61" s="1" t="s">
         <v>1533</v>
@@ -13404,10 +13411,10 @@
         <v>27</v>
       </c>
       <c r="W76" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X76" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X76" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y76" s="1" t="s">
         <v>27</v>
@@ -14835,7 +14842,7 @@
         <v>1591</v>
       </c>
       <c r="Y91" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z91" s="1" t="s">
         <v>1533</v>
@@ -15141,98 +15148,98 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="95" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A95" s="5" t="s">
+    <row r="95" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="D95" s="5" t="s">
+      <c r="D95" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E95" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F95" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="G95" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="H95" s="7" t="s">
+      <c r="H95" s="10" t="s">
         <v>1594</v>
       </c>
-      <c r="I95" s="5" t="s">
+      <c r="I95" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="J95" s="5" t="s">
+      <c r="J95" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="K95" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L95" s="5" t="s">
+      <c r="K95" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L95" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="M95" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N95" s="5" t="s">
+      <c r="M95" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N95" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="O95" s="5" t="s">
+      <c r="O95" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="P95" s="5" t="s">
+      <c r="P95" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="Q95" s="5" t="s">
+      <c r="Q95" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="R95" s="5" t="s">
+      <c r="R95" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="S95" s="5" t="s">
+      <c r="S95" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="T95" s="5" t="s">
+      <c r="T95" s="9" t="s">
         <v>1542</v>
       </c>
-      <c r="U95" s="5" t="s">
+      <c r="U95" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="V95" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="W95" s="5" t="s">
+      <c r="V95" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="W95" s="11" t="s">
+        <v>1673</v>
+      </c>
+      <c r="X95" s="9" t="s">
         <v>1747</v>
       </c>
-      <c r="X95" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y95" s="5" t="s">
+      <c r="Y95" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="Z95" s="5" t="s">
+      <c r="Z95" s="9" t="s">
         <v>1533</v>
       </c>
-      <c r="AA95" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB95" s="5" t="s">
+      <c r="AA95" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB95" s="9" t="s">
         <v>1534</v>
       </c>
-      <c r="AC95" s="5" t="s">
+      <c r="AC95" s="9" t="s">
         <v>1540</v>
       </c>
-      <c r="AD95" s="5" t="s">
+      <c r="AD95" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="AE95" s="5" t="s">
+      <c r="AE95" s="9" t="s">
         <v>1588</v>
       </c>
     </row>
@@ -16254,10 +16261,10 @@
         <v>27</v>
       </c>
       <c r="W106" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="X106" s="1" t="s">
         <v>1487</v>
-      </c>
-      <c r="X106" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y106" s="1" t="s">
         <v>266</v>
@@ -19199,10 +19206,10 @@
         <v>27</v>
       </c>
       <c r="W137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X137" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="X137" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y137" s="1" t="s">
         <v>1538</v>
@@ -19389,10 +19396,10 @@
         <v>27</v>
       </c>
       <c r="W139" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X139" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X139" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y139" s="1" t="s">
         <v>27</v>
@@ -20719,9 +20726,11 @@
         <v>27</v>
       </c>
       <c r="W153" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="X153" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="X153" s="1"/>
       <c r="Y153" s="1" t="s">
         <v>27</v>
       </c>
@@ -22426,8 +22435,8 @@
       <c r="V171" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="W171" s="5" t="s">
-        <v>1750</v>
+      <c r="W171" s="9" t="s">
+        <v>1759</v>
       </c>
       <c r="X171" s="5" t="s">
         <v>1495</v>
@@ -22718,7 +22727,7 @@
         <v>1497</v>
       </c>
       <c r="Y174" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z174" s="1" t="s">
         <v>1533</v>
@@ -23193,7 +23202,7 @@
         <v>1501</v>
       </c>
       <c r="Y179" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z179" s="1" t="s">
         <v>1533</v>
@@ -23478,7 +23487,7 @@
         <v>589</v>
       </c>
       <c r="Y182" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z182" s="1" t="s">
         <v>1533</v>
@@ -25684,28 +25693,28 @@
     </row>
     <row r="206" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>1752</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
         <v>1753</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>1754</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E206" s="1" t="s">
+        <v>1754</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H206" s="1" t="s">
         <v>1755</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>1756</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>27</v>
@@ -25753,7 +25762,7 @@
         <v>1744</v>
       </c>
       <c r="X206" s="1" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="Y206" s="1" t="s">
         <v>1611</v>
@@ -25774,7 +25783,7 @@
         <v>69</v>
       </c>
       <c r="AE206" s="1" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="207" spans="1:31" x14ac:dyDescent="0.45">
@@ -28600,10 +28609,10 @@
         <v>27</v>
       </c>
       <c r="W236" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X236" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X236" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y236" s="1" t="s">
         <v>27</v>
@@ -28701,7 +28710,7 @@
         <v>736</v>
       </c>
       <c r="Y237" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z237" s="1" t="s">
         <v>1533</v>
@@ -29838,10 +29847,10 @@
         <v>1742</v>
       </c>
       <c r="X249" s="1" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="Y249" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z249" s="1" t="s">
         <v>1533</v>
@@ -30310,10 +30319,10 @@
         <v>27</v>
       </c>
       <c r="W254" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X254" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X254" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y254" s="1" t="s">
         <v>27</v>
@@ -32494,8 +32503,8 @@
       <c r="V277" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W277" s="1" t="s">
-        <v>1750</v>
+      <c r="W277" s="9" t="s">
+        <v>1759</v>
       </c>
       <c r="X277" s="1" t="s">
         <v>1509</v>
@@ -33444,8 +33453,8 @@
       <c r="V287" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W287" s="1" t="s">
-        <v>1750</v>
+      <c r="W287" s="9" t="s">
+        <v>1759</v>
       </c>
       <c r="X287" s="1" t="s">
         <v>884</v>
@@ -33635,10 +33644,10 @@
         <v>27</v>
       </c>
       <c r="W289" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X289" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X289" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y289" s="1" t="s">
         <v>27</v>
@@ -33831,7 +33840,7 @@
         <v>1489</v>
       </c>
       <c r="Y291" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z291" s="1" t="s">
         <v>1533</v>
@@ -34395,10 +34404,10 @@
         <v>27</v>
       </c>
       <c r="W297" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X297" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X297" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y297" s="1" t="s">
         <v>27</v>
@@ -34781,7 +34790,7 @@
         <v>27</v>
       </c>
       <c r="Y301" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z301" s="1" t="s">
         <v>1533</v>
@@ -35725,10 +35734,10 @@
         <v>27</v>
       </c>
       <c r="W311" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X311" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X311" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y311" s="1" t="s">
         <v>27</v>
@@ -35752,98 +35761,98 @@
         <v>951</v>
       </c>
     </row>
-    <row r="312" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A312" s="5" t="s">
+    <row r="312" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A312" s="9" t="s">
         <v>937</v>
       </c>
-      <c r="B312" s="5" t="s">
+      <c r="B312" s="9" t="s">
         <v>938</v>
       </c>
-      <c r="C312" s="5" t="s">
+      <c r="C312" s="9" t="s">
         <v>939</v>
       </c>
-      <c r="D312" s="5" t="s">
+      <c r="D312" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E312" s="5" t="s">
+      <c r="E312" s="9" t="s">
         <v>949</v>
       </c>
-      <c r="F312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H312" s="5" t="s">
+      <c r="F312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H312" s="9" t="s">
         <v>793</v>
       </c>
-      <c r="I312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L312" s="5" t="s">
+      <c r="I312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L312" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="M312" s="5">
+      <c r="M312" s="9">
         <v>1</v>
       </c>
-      <c r="N312" s="5" t="s">
+      <c r="N312" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O312" s="5" t="s">
+      <c r="O312" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="P312" s="5" t="s">
+      <c r="P312" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="Q312" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="R312" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="T312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="U312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="V312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="W312" s="5" t="s">
+      <c r="Q312" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R312" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="T312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="U312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="V312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="W312" s="9" t="s">
+        <v>1759</v>
+      </c>
+      <c r="X312" s="9" t="s">
         <v>1513</v>
       </c>
-      <c r="X312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y312" s="5" t="s">
+      <c r="Y312" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="Z312" s="5" t="s">
+      <c r="Z312" s="9" t="s">
         <v>1533</v>
       </c>
-      <c r="AA312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD312" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE312" s="5" t="s">
+      <c r="AA312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD312" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE312" s="9" t="s">
         <v>952</v>
       </c>
     </row>
@@ -36681,7 +36690,7 @@
         <v>27</v>
       </c>
       <c r="Y321" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z321" s="1" t="s">
         <v>1533</v>
@@ -39246,7 +39255,7 @@
         <v>1489</v>
       </c>
       <c r="Y348" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Z348" s="1" t="s">
         <v>1533</v>
@@ -40855,10 +40864,10 @@
         <v>27</v>
       </c>
       <c r="W365" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X365" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X365" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y365" s="1" t="s">
         <v>27</v>
@@ -45414,8 +45423,8 @@
       <c r="V413" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W413" s="1" t="s">
-        <v>1750</v>
+      <c r="W413" s="9" t="s">
+        <v>1759</v>
       </c>
       <c r="X413" s="1" t="s">
         <v>1519</v>
@@ -47220,10 +47229,10 @@
         <v>27</v>
       </c>
       <c r="W432" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="X432" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="X432" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y432" s="1" t="s">
         <v>27</v>
@@ -52758,7 +52767,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="Y1:Y490" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AE490" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
